--- a/Laboratorio/esperienza2/prove/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/prove/esperienza2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\Documents\UNIVERSITA'\III ANNO\Laboratorio-di-Ottica\Laboratorio\esperienza2\prove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D42A97-CD16-4D9D-A3D7-74ACB0FEF89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C939CBC3-6977-412D-B250-39F1B618594F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t xml:space="preserve"> L</t>
   </si>
@@ -1308,7 +1308,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$H$1</c:f>
+              <c:f>Dati!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1343,7 +1343,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$130</c:f>
+              <c:f>Dati!$F$2:$F$130</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="129"/>
@@ -1700,7 +1700,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$H$2:$H$130</c:f>
+              <c:f>Dati!$G$2:$G$130</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="129"/>
@@ -2304,12 +2304,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$L$1</c:f>
+              <c:f>Dati!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>q</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2339,715 +2336,15 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$K$2:$K$130</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="129"/>
-                <c:pt idx="0">
-                  <c:v>232.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>233.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>234.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>235.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>236.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>237.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>238.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>239.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>240.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>241.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>242.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>243.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>244.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>245.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>246.5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>247.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>248.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>249.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>250.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>251.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>252.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>253.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>254.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>255.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>256.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>257.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>258.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>259.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>260.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>261.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>262.5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>263.5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>264.5</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>265.5</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>267.5</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>269.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>271.5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>273.5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>275.5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>277.5</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>280.5</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>281.5</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>282.5</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>283.5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>284.5</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>285.5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>286.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>287.5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>288.5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>289.5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>290.5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>291.5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>292.5</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>293.5</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>294.5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>295.5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>297.5</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>299.5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>301.5</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>306.5</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>311.5</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>316.5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>321.5</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>326.5</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>331.5</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>336.5</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>341.5</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>346.5</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>351.5</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>356.5</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>361.5</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>366.5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>371.5</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>376.5</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>381.5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>386.5</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>391.5</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>396.5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>401.5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>406.5</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>411.5</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>416.5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>421.5</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>426.5</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>431.5</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>441.5</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>451.5</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>461.5</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>471.5</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>481.5</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>491.5</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>501.5</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>511.5</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>521.5</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>531.5</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>541.5</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>551.5</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>561.5</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>571.5</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>581.5</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>601.5</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>621.5</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>641.5</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>661.5</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>681.5</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>731.5</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>781.5</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>831.5</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>881.5</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>981.5</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>1081.5</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>1181.5</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>1281.5</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1381.5</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1481.5</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1631.5</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Dati!#REF!</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$L$2:$L$130</c:f>
+              <c:f>Dati!$J$2:$J$130</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="129"/>
-                <c:pt idx="0">
-                  <c:v>1568.3956187495346</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1522.5370809527169</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1514.6242539025059</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1448.3063104970304</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1416.5366742321485</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1382.5913567979078</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1352.1281761548335</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1316.1424428014113</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1292.227285364251</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1256.5927696390497</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1229.4369333409034</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1216.4864065569802</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1177.9033231647918</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1160.0582035807654</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1133.0499991071747</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1126.0222379861807</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1106.6729262437348</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1086.0862804408871</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1064.1044902928011</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1047.7439145531227</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1026.778442658594</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1014.7575412000506</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>997.11005813176394</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>986.22185054767601</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>967.27810396229347</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>951.76583136790714</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>935.85143124581282</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>921.30762088650704</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>913.35673062950491</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>902.32259118873526</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>887.86164853068794</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>881.38319878055563</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>867.38188114877971</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>856.31606834535955</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>835.91280800603022</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>817.41771703364043</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>799.38993948084385</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>783.90908707552876</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>767.38704148583633</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>754.43717152141676</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>729.87584121464397</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>725.36750970623939</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>717.87462501523669</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>706.45534290239664</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>698.43410346668998</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>697.43410346668998</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>688.94979793160257</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>684.47166206396048</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>680.95909006382692</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>673.46326825153972</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>668.46311824386737</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>665.45383522701468</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>656.48955641615851</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>653.96694158426715</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>647.98130822981193</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>644.98126932838807</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>634.9664212342426</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>626.47768066658602</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>614.96584783011167</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>595.97345573965447</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>578.48887966849986</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>549</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>529</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>523</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>512</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>499</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>489</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>479</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>468</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>458</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>451</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>445</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>436</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>428</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>420</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>413</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>404</c:v>
-                </c:pt>
-                <c:pt idx="77" formatCode="#,##0.00">
-                  <c:v>396</c:v>
-                </c:pt>
-                <c:pt idx="78" formatCode="#,##0.00">
-                  <c:v>393</c:v>
-                </c:pt>
-                <c:pt idx="79" formatCode="#,##0.00">
-                  <c:v>391</c:v>
-                </c:pt>
-                <c:pt idx="80" formatCode="#,##0.00">
-                  <c:v>388</c:v>
-                </c:pt>
-                <c:pt idx="81" formatCode="#,##0.00">
-                  <c:v>383</c:v>
-                </c:pt>
-                <c:pt idx="82" formatCode="#,##0.00">
-                  <c:v>380</c:v>
-                </c:pt>
-                <c:pt idx="83" formatCode="#,##0.00">
-                  <c:v>376</c:v>
-                </c:pt>
-                <c:pt idx="84" formatCode="#,##0.00">
-                  <c:v>372</c:v>
-                </c:pt>
-                <c:pt idx="85" formatCode="#,##0.00">
-                  <c:v>363</c:v>
-                </c:pt>
-                <c:pt idx="86" formatCode="#,##0.00">
-                  <c:v>358</c:v>
-                </c:pt>
-                <c:pt idx="87" formatCode="#,##0.00">
-                  <c:v>351</c:v>
-                </c:pt>
-                <c:pt idx="88" formatCode="#,##0.00">
-                  <c:v>336</c:v>
-                </c:pt>
-                <c:pt idx="89" formatCode="#,##0.00">
-                  <c:v>341</c:v>
-                </c:pt>
-                <c:pt idx="90" formatCode="#,##0.00">
-                  <c:v>336</c:v>
-                </c:pt>
-                <c:pt idx="91" formatCode="#,##0.00">
-                  <c:v>331</c:v>
-                </c:pt>
-                <c:pt idx="92" formatCode="#,##0.00">
-                  <c:v>326</c:v>
-                </c:pt>
-                <c:pt idx="93" formatCode="#,##0.00">
-                  <c:v>321</c:v>
-                </c:pt>
-                <c:pt idx="94" formatCode="#,##0.00">
-                  <c:v>316</c:v>
-                </c:pt>
-                <c:pt idx="95" formatCode="#,##0.00">
-                  <c:v>316</c:v>
-                </c:pt>
-                <c:pt idx="96" formatCode="#,##0.00">
-                  <c:v>311</c:v>
-                </c:pt>
-                <c:pt idx="97" formatCode="#,##0.00">
-                  <c:v>308</c:v>
-                </c:pt>
-                <c:pt idx="98" formatCode="#,##0.00">
-                  <c:v>306</c:v>
-                </c:pt>
-                <c:pt idx="99" formatCode="#,##0.00">
-                  <c:v>301</c:v>
-                </c:pt>
-                <c:pt idx="100" formatCode="#,##0.00">
-                  <c:v>296</c:v>
-                </c:pt>
-                <c:pt idx="101" formatCode="#,##0.00">
-                  <c:v>290</c:v>
-                </c:pt>
-                <c:pt idx="102" formatCode="#,##0.00">
-                  <c:v>289</c:v>
-                </c:pt>
-                <c:pt idx="103" formatCode="#,##0.00">
-                  <c:v>283</c:v>
-                </c:pt>
-                <c:pt idx="104" formatCode="#,##0.00">
-                  <c:v>281</c:v>
-                </c:pt>
-                <c:pt idx="105" formatCode="#,##0.00">
-                  <c:v>271</c:v>
-                </c:pt>
-                <c:pt idx="106" formatCode="#,##0.00">
-                  <c:v>264</c:v>
-                </c:pt>
-                <c:pt idx="107" formatCode="#,##0.00">
-                  <c:v>259</c:v>
-                </c:pt>
-                <c:pt idx="108" formatCode="#,##0.00">
-                  <c:v>255</c:v>
-                </c:pt>
-                <c:pt idx="109" formatCode="#,##0.00">
-                  <c:v>246</c:v>
-                </c:pt>
-                <c:pt idx="110" formatCode="#,##0.00">
-                  <c:v>240</c:v>
-                </c:pt>
-                <c:pt idx="111" formatCode="#,##0.00">
-                  <c:v>236</c:v>
-                </c:pt>
-                <c:pt idx="112" formatCode="#,##0.00">
-                  <c:v>233</c:v>
-                </c:pt>
-                <c:pt idx="113" formatCode="#,##0.00">
-                  <c:v>229</c:v>
-                </c:pt>
-                <c:pt idx="114" formatCode="#,##0.00">
-                  <c:v>227</c:v>
-                </c:pt>
-                <c:pt idx="115" formatCode="#,##0.00">
-                  <c:v>223</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4958,13 +4255,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>552822</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>115046</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>44824</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>59763</xdr:rowOff>
@@ -4994,13 +4291,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>315870</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>34024</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>325581</xdr:colOff>
       <xdr:row>110</xdr:row>
       <xdr:rowOff>69273</xdr:rowOff>
@@ -9582,18 +8879,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.44140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="6" width="12.44140625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="8" customWidth="1"/>
-    <col min="9" max="12" width="12.44140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="8" customWidth="1"/>
+    <col min="8" max="10" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
@@ -9609,26 +8906,20 @@
       <c r="E1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>251</v>
       </c>
@@ -9644,26 +8935,21 @@
       <c r="E2" s="8">
         <v>11.258330249197703</v>
       </c>
-      <c r="G2" s="1">
+      <c r="F2" s="1">
         <v>232.5</v>
       </c>
-      <c r="H2" s="8">
+      <c r="G2" s="8">
         <v>1568.3956187495346</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I2" s="1">
         <v>11.258330249197703</v>
       </c>
-      <c r="J2" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K2" s="1">
-        <v>232.5</v>
-      </c>
-      <c r="L2" s="8">
-        <v>1568.3956187495346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>252</v>
       </c>
@@ -9679,26 +8965,21 @@
       <c r="E3" s="8">
         <v>33.774990747593108</v>
       </c>
-      <c r="G3" s="1">
+      <c r="F3" s="1">
         <v>233.5</v>
       </c>
-      <c r="H3" s="8">
+      <c r="G3" s="8">
         <v>1522.5370809527169</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I3" s="1">
         <v>33.774990747593108</v>
       </c>
-      <c r="J3" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K3" s="1">
-        <v>233.5</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1522.5370809527169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>253</v>
       </c>
@@ -9714,26 +8995,21 @@
       <c r="E4" s="8">
         <v>47.0540469389545</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F4" s="1">
         <v>234.5</v>
       </c>
-      <c r="H4" s="8">
+      <c r="G4" s="8">
         <v>1514.6242539025059</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I4" s="1">
         <v>47.0540469389545</v>
       </c>
-      <c r="J4" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K4" s="1">
-        <v>234.5</v>
-      </c>
-      <c r="L4" s="8">
-        <v>1514.6242539025059</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>254</v>
       </c>
@@ -9749,26 +9025,21 @@
       <c r="E5" s="8">
         <v>43.878620458411561</v>
       </c>
-      <c r="G5" s="1">
+      <c r="F5" s="1">
         <v>235.5</v>
       </c>
-      <c r="H5" s="8">
+      <c r="G5" s="8">
         <v>1448.3063104970304</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I5" s="1">
         <v>43.878620458411561</v>
       </c>
-      <c r="J5" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K5" s="1">
-        <v>235.5</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1448.3063104970304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>255</v>
       </c>
@@ -9784,26 +9055,21 @@
       <c r="E6" s="8">
         <v>40.414518843273804</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="1">
         <v>236.5</v>
       </c>
-      <c r="H6" s="8">
+      <c r="G6" s="8">
         <v>1416.5366742321485</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I6" s="1">
         <v>40.414518843273804</v>
       </c>
-      <c r="J6" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K6" s="1">
-        <v>236.5</v>
-      </c>
-      <c r="L6" s="8">
-        <v>1416.5366742321485</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>256</v>
       </c>
@@ -9819,26 +9085,21 @@
       <c r="E7" s="8">
         <v>39.259818304894551</v>
       </c>
-      <c r="G7" s="1">
+      <c r="F7" s="1">
         <v>237.5</v>
       </c>
-      <c r="H7" s="8">
+      <c r="G7" s="8">
         <v>1382.5913567979078</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I7" s="1">
         <v>39.259818304894551</v>
       </c>
-      <c r="J7" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K7" s="1">
-        <v>237.5</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1382.5913567979078</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>257</v>
       </c>
@@ -9854,26 +9115,21 @@
       <c r="E8" s="8">
         <v>38.393792901110118</v>
       </c>
-      <c r="G8" s="1">
+      <c r="F8" s="1">
         <v>238.5</v>
       </c>
-      <c r="H8" s="8">
+      <c r="G8" s="8">
         <v>1352.1281761548335</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I8" s="1">
         <v>38.393792901110118</v>
       </c>
-      <c r="J8" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K8" s="1">
-        <v>238.5</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1352.1281761548335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>258</v>
       </c>
@@ -9889,26 +9145,21 @@
       <c r="E9" s="8">
         <v>30.02221399786054</v>
       </c>
-      <c r="G9" s="1">
+      <c r="F9" s="1">
         <v>239.5</v>
       </c>
-      <c r="H9" s="8">
+      <c r="G9" s="8">
         <v>1316.1424428014113</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I9" s="1">
         <v>30.02221399786054</v>
       </c>
-      <c r="J9" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K9" s="1">
-        <v>239.5</v>
-      </c>
-      <c r="L9" s="8">
-        <v>1316.1424428014113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>259</v>
       </c>
@@ -9924,26 +9175,21 @@
       <c r="E10" s="8">
         <v>28.290163190291665</v>
       </c>
-      <c r="G10" s="1">
+      <c r="F10" s="1">
         <v>240.5</v>
       </c>
-      <c r="H10" s="8">
+      <c r="G10" s="8">
         <v>1292.227285364251</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I10" s="1">
         <v>28.290163190291665</v>
       </c>
-      <c r="J10" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K10" s="1">
-        <v>240.5</v>
-      </c>
-      <c r="L10" s="8">
-        <v>1292.227285364251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>260</v>
       </c>
@@ -9959,26 +9205,21 @@
       <c r="E11" s="8">
         <v>30.310889132455355</v>
       </c>
-      <c r="G11" s="1">
+      <c r="F11" s="1">
         <v>241.5</v>
       </c>
-      <c r="H11" s="8">
+      <c r="G11" s="8">
         <v>1256.5927696390497</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I11" s="1">
         <v>30.310889132455355</v>
       </c>
-      <c r="J11" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K11" s="1">
-        <v>241.5</v>
-      </c>
-      <c r="L11" s="8">
-        <v>1256.5927696390497</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>261</v>
       </c>
@@ -9994,26 +9235,21 @@
       <c r="E12" s="8">
         <v>23.671361036774659</v>
       </c>
-      <c r="G12" s="1">
+      <c r="F12" s="1">
         <v>242.5</v>
       </c>
-      <c r="H12" s="8">
+      <c r="G12" s="8">
         <v>1229.4369333409034</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I12" s="1">
         <v>23.671361036774659</v>
       </c>
-      <c r="J12" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K12" s="1">
-        <v>242.5</v>
-      </c>
-      <c r="L12" s="8">
-        <v>1229.4369333409034</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>262</v>
       </c>
@@ -10029,26 +9265,21 @@
       <c r="E13" s="8">
         <v>22.516660498395407</v>
       </c>
-      <c r="G13" s="1">
+      <c r="F13" s="1">
         <v>243.5</v>
       </c>
-      <c r="H13" s="8">
+      <c r="G13" s="8">
         <v>1216.4864065569802</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I13" s="1">
         <v>22.516660498395407</v>
       </c>
-      <c r="J13" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K13" s="1">
-        <v>243.5</v>
-      </c>
-      <c r="L13" s="8">
-        <v>1216.4864065569802</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>263</v>
       </c>
@@ -10064,26 +9295,21 @@
       <c r="E14" s="8">
         <v>23.96003617136947</v>
       </c>
-      <c r="G14" s="1">
+      <c r="F14" s="1">
         <v>244.5</v>
       </c>
-      <c r="H14" s="8">
+      <c r="G14" s="8">
         <v>1177.9033231647918</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I14" s="1">
         <v>23.96003617136947</v>
       </c>
-      <c r="J14" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K14" s="1">
-        <v>244.5</v>
-      </c>
-      <c r="L14" s="8">
-        <v>1177.9033231647918</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>264</v>
       </c>
@@ -10099,26 +9325,21 @@
       <c r="E15" s="8">
         <v>20.495934556231717</v>
       </c>
-      <c r="G15" s="1">
+      <c r="F15" s="1">
         <v>245.5</v>
       </c>
-      <c r="H15" s="8">
+      <c r="G15" s="8">
         <v>1160.0582035807654</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I15" s="1">
         <v>20.495934556231717</v>
       </c>
-      <c r="J15" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K15" s="1">
-        <v>245.5</v>
-      </c>
-      <c r="L15" s="8">
-        <v>1160.0582035807654</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>265</v>
       </c>
@@ -10134,26 +9355,21 @@
       <c r="E16" s="8">
         <v>20.495934556231717</v>
       </c>
-      <c r="G16" s="1">
+      <c r="F16" s="1">
         <v>246.5</v>
       </c>
-      <c r="H16" s="8">
+      <c r="G16" s="8">
         <v>1133.0499991071747</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I16" s="1">
         <v>20.495934556231717</v>
       </c>
-      <c r="J16" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K16" s="1">
-        <v>246.5</v>
-      </c>
-      <c r="L16" s="8">
-        <v>1133.0499991071747</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>266</v>
       </c>
@@ -10169,26 +9385,21 @@
       <c r="E17" s="8">
         <v>21.073284825421343</v>
       </c>
-      <c r="G17" s="1">
+      <c r="F17" s="1">
         <v>247.5</v>
       </c>
-      <c r="H17" s="8">
+      <c r="G17" s="8">
         <v>1126.0222379861807</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I17" s="1">
         <v>21.073284825421343</v>
       </c>
-      <c r="J17" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K17" s="1">
-        <v>247.5</v>
-      </c>
-      <c r="L17" s="8">
-        <v>1126.0222379861807</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>267</v>
       </c>
@@ -10204,26 +9415,21 @@
       <c r="E18" s="8">
         <v>17.320508075688775</v>
       </c>
-      <c r="G18" s="1">
+      <c r="F18" s="1">
         <v>248.5</v>
       </c>
-      <c r="H18" s="8">
+      <c r="G18" s="8">
         <v>1106.6729262437348</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I18" s="1">
         <v>17.320508075688775</v>
       </c>
-      <c r="J18" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K18" s="1">
-        <v>248.5</v>
-      </c>
-      <c r="L18" s="8">
-        <v>1106.6729262437348</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>268</v>
       </c>
@@ -10239,26 +9445,21 @@
       <c r="E19" s="8">
         <v>19.341234017852464</v>
       </c>
-      <c r="G19" s="1">
+      <c r="F19" s="1">
         <v>249.5</v>
       </c>
-      <c r="H19" s="8">
+      <c r="G19" s="8">
         <v>1086.0862804408871</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I19" s="1">
         <v>19.341234017852464</v>
       </c>
-      <c r="J19" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K19" s="1">
-        <v>249.5</v>
-      </c>
-      <c r="L19" s="8">
-        <v>1086.0862804408871</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>269</v>
       </c>
@@ -10274,26 +9475,21 @@
       <c r="E20" s="8">
         <v>18.763883748662838</v>
       </c>
-      <c r="G20" s="1">
+      <c r="F20" s="1">
         <v>250.5</v>
       </c>
-      <c r="H20" s="8">
+      <c r="G20" s="8">
         <v>1064.1044902928011</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I20" s="1">
         <v>18.763883748662838</v>
       </c>
-      <c r="J20" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K20" s="1">
-        <v>250.5</v>
-      </c>
-      <c r="L20" s="8">
-        <v>1064.1044902928011</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>270</v>
       </c>
@@ -10309,26 +9505,21 @@
       <c r="E21" s="8">
         <v>15.01110699893027</v>
       </c>
-      <c r="G21" s="1">
+      <c r="F21" s="1">
         <v>251.5</v>
       </c>
-      <c r="H21" s="8">
+      <c r="G21" s="8">
         <v>1047.7439145531227</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I21" s="1">
         <v>15.01110699893027</v>
       </c>
-      <c r="J21" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K21" s="1">
-        <v>251.5</v>
-      </c>
-      <c r="L21" s="8">
-        <v>1047.7439145531227</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>271</v>
       </c>
@@ -10344,26 +9535,21 @@
       <c r="E22" s="8">
         <v>13.856406460551019</v>
       </c>
-      <c r="G22" s="1">
+      <c r="F22" s="1">
         <v>252.5</v>
       </c>
-      <c r="H22" s="8">
+      <c r="G22" s="8">
         <v>1026.778442658594</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I22" s="1">
         <v>13.856406460551019</v>
       </c>
-      <c r="J22" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K22" s="1">
-        <v>252.5</v>
-      </c>
-      <c r="L22" s="8">
-        <v>1026.778442658594</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>272</v>
       </c>
@@ -10379,26 +9565,21 @@
       <c r="E23" s="8">
         <v>14.433756729740645</v>
       </c>
-      <c r="G23" s="1">
+      <c r="F23" s="1">
         <v>253.5</v>
       </c>
-      <c r="H23" s="8">
+      <c r="G23" s="8">
         <v>1014.7575412000506</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I23" s="1">
         <v>14.433756729740645</v>
       </c>
-      <c r="J23" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K23" s="1">
-        <v>253.5</v>
-      </c>
-      <c r="L23" s="8">
-        <v>1014.7575412000506</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>273</v>
       </c>
@@ -10414,26 +9595,21 @@
       <c r="E24" s="8">
         <v>18.186533479473212</v>
       </c>
-      <c r="G24" s="1">
+      <c r="F24" s="1">
         <v>254.5</v>
       </c>
-      <c r="H24" s="8">
+      <c r="G24" s="8">
         <v>997.11005813176394</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I24" s="1">
         <v>18.186533479473212</v>
       </c>
-      <c r="J24" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K24" s="1">
-        <v>254.5</v>
-      </c>
-      <c r="L24" s="8">
-        <v>997.11005813176394</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>274</v>
       </c>
@@ -10449,26 +9625,21 @@
       <c r="E25" s="8">
         <v>15.299782133525083</v>
       </c>
-      <c r="G25" s="1">
+      <c r="F25" s="1">
         <v>255.5</v>
       </c>
-      <c r="H25" s="8">
+      <c r="G25" s="8">
         <v>986.22185054767601</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I25" s="1">
         <v>15.299782133525083</v>
       </c>
-      <c r="J25" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K25" s="1">
-        <v>255.5</v>
-      </c>
-      <c r="L25" s="8">
-        <v>986.22185054767601</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>275</v>
       </c>
@@ -10484,26 +9655,21 @@
       <c r="E26" s="8">
         <v>13.567731325956206</v>
       </c>
-      <c r="G26" s="1">
+      <c r="F26" s="1">
         <v>256.5</v>
       </c>
-      <c r="H26" s="8">
+      <c r="G26" s="8">
         <v>967.27810396229347</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I26" s="1">
         <v>13.567731325956206</v>
       </c>
-      <c r="J26" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K26" s="1">
-        <v>256.5</v>
-      </c>
-      <c r="L26" s="8">
-        <v>967.27810396229347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>276</v>
       </c>
@@ -10519,26 +9685,21 @@
       <c r="E27" s="8">
         <v>13.856406460551019</v>
       </c>
-      <c r="G27" s="1">
+      <c r="F27" s="1">
         <v>257.5</v>
       </c>
-      <c r="H27" s="8">
+      <c r="G27" s="8">
         <v>951.76583136790714</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I27" s="1">
         <v>13.856406460551019</v>
       </c>
-      <c r="J27" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K27" s="1">
-        <v>257.5</v>
-      </c>
-      <c r="L27" s="8">
-        <v>951.76583136790714</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>277</v>
       </c>
@@ -10554,26 +9715,21 @@
       <c r="E28" s="8">
         <v>10.96965511460289</v>
       </c>
-      <c r="G28" s="1">
+      <c r="F28" s="1">
         <v>258.5</v>
       </c>
-      <c r="H28" s="8">
+      <c r="G28" s="8">
         <v>935.85143124581282</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I28" s="1">
         <v>10.96965511460289</v>
       </c>
-      <c r="J28" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K28" s="1">
-        <v>258.5</v>
-      </c>
-      <c r="L28" s="8">
-        <v>935.85143124581282</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>278</v>
       </c>
@@ -10589,26 +9745,21 @@
       <c r="E29" s="8">
         <v>12.413030787576954</v>
       </c>
-      <c r="G29" s="1">
+      <c r="F29" s="1">
         <v>259.5</v>
       </c>
-      <c r="H29" s="8">
+      <c r="G29" s="8">
         <v>921.30762088650704</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I29" s="1">
         <v>12.413030787576954</v>
       </c>
-      <c r="J29" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K29" s="1">
-        <v>259.5</v>
-      </c>
-      <c r="L29" s="8">
-        <v>921.30762088650704</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>279</v>
       </c>
@@ -10624,26 +9775,21 @@
       <c r="E30" s="8">
         <v>10.680979980008077</v>
       </c>
-      <c r="G30" s="1">
+      <c r="F30" s="1">
         <v>260.5</v>
       </c>
-      <c r="H30" s="8">
+      <c r="G30" s="8">
         <v>913.35673062950491</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I30" s="1">
         <v>10.680979980008077</v>
       </c>
-      <c r="J30" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K30" s="1">
-        <v>260.5</v>
-      </c>
-      <c r="L30" s="8">
-        <v>913.35673062950491</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>280</v>
       </c>
@@ -10659,26 +9805,21 @@
       <c r="E31" s="8">
         <v>11.835680518387329</v>
       </c>
-      <c r="G31" s="1">
+      <c r="F31" s="1">
         <v>261.5</v>
       </c>
-      <c r="H31" s="8">
+      <c r="G31" s="8">
         <v>902.32259118873526</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I31" s="1">
         <v>11.835680518387329</v>
       </c>
-      <c r="J31" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K31" s="1">
-        <v>261.5</v>
-      </c>
-      <c r="L31" s="8">
-        <v>902.32259118873526</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>281</v>
       </c>
@@ -10694,26 +9835,21 @@
       <c r="E32" s="8">
         <v>10.392304845413264</v>
       </c>
-      <c r="G32" s="1">
+      <c r="F32" s="1">
         <v>262.5</v>
       </c>
-      <c r="H32" s="8">
+      <c r="G32" s="8">
         <v>887.86164853068794</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I32" s="1">
         <v>10.392304845413264</v>
       </c>
-      <c r="J32" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K32" s="1">
-        <v>262.5</v>
-      </c>
-      <c r="L32" s="8">
-        <v>887.86164853068794</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>282</v>
       </c>
@@ -10729,26 +9865,21 @@
       <c r="E33" s="8">
         <v>9.5262794416288248</v>
       </c>
-      <c r="G33" s="1">
+      <c r="F33" s="1">
         <v>263.5</v>
       </c>
-      <c r="H33" s="8">
+      <c r="G33" s="8">
         <v>881.38319878055563</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I33" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J33" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K33" s="1">
-        <v>263.5</v>
-      </c>
-      <c r="L33" s="8">
-        <v>881.38319878055563</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>283</v>
       </c>
@@ -10764,26 +9895,21 @@
       <c r="E34" s="8">
         <v>9.5262794416288248</v>
       </c>
-      <c r="G34" s="1">
+      <c r="F34" s="1">
         <v>264.5</v>
       </c>
-      <c r="H34" s="8">
+      <c r="G34" s="8">
         <v>867.38188114877971</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I34" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J34" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K34" s="1">
-        <v>264.5</v>
-      </c>
-      <c r="L34" s="8">
-        <v>867.38188114877971</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>284</v>
       </c>
@@ -10799,26 +9925,21 @@
       <c r="E35" s="8">
         <v>11.835680518387329</v>
       </c>
-      <c r="G35" s="1">
+      <c r="F35" s="1">
         <v>265.5</v>
       </c>
-      <c r="H35" s="8">
+      <c r="G35" s="8">
         <v>856.31606834535955</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I35" s="1">
         <v>11.835680518387329</v>
       </c>
-      <c r="J35" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K35" s="1">
-        <v>265.5</v>
-      </c>
-      <c r="L35" s="8">
-        <v>856.31606834535955</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>286</v>
       </c>
@@ -10834,26 +9955,21 @@
       <c r="E36" s="8">
         <v>8.0829037686547611</v>
       </c>
-      <c r="G36" s="1">
+      <c r="F36" s="1">
         <v>267.5</v>
       </c>
-      <c r="H36" s="8">
+      <c r="G36" s="8">
         <v>835.91280800603022</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I36" s="1">
         <v>8.0829037686547611</v>
       </c>
-      <c r="J36" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K36" s="1">
-        <v>267.5</v>
-      </c>
-      <c r="L36" s="8">
-        <v>835.91280800603022</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>288</v>
       </c>
@@ -10869,26 +9985,21 @@
       <c r="E37" s="8">
         <v>7.794228634059948</v>
       </c>
-      <c r="G37" s="1">
+      <c r="F37" s="1">
         <v>269.5</v>
       </c>
-      <c r="H37" s="8">
+      <c r="G37" s="8">
         <v>817.41771703364043</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I37" s="1">
         <v>7.794228634059948</v>
       </c>
-      <c r="J37" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K37" s="1">
-        <v>269.5</v>
-      </c>
-      <c r="L37" s="8">
-        <v>817.41771703364043</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>290</v>
       </c>
@@ -10904,26 +10015,21 @@
       <c r="E38" s="8">
         <v>8.9489291724392004</v>
       </c>
-      <c r="G38" s="1">
+      <c r="F38" s="1">
         <v>271.5</v>
       </c>
-      <c r="H38" s="8">
+      <c r="G38" s="8">
         <v>799.38993948084385</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I38" s="1">
         <v>8.9489291724392004</v>
       </c>
-      <c r="J38" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K38" s="1">
-        <v>271.5</v>
-      </c>
-      <c r="L38" s="8">
-        <v>799.38993948084385</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>292</v>
       </c>
@@ -10939,26 +10045,21 @@
       <c r="E39" s="8">
         <v>8.0829037686547611</v>
       </c>
-      <c r="G39" s="1">
+      <c r="F39" s="1">
         <v>273.5</v>
       </c>
-      <c r="H39" s="8">
+      <c r="G39" s="8">
         <v>783.90908707552876</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I39" s="1">
         <v>8.0829037686547611</v>
       </c>
-      <c r="J39" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K39" s="1">
-        <v>273.5</v>
-      </c>
-      <c r="L39" s="8">
-        <v>783.90908707552876</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>294</v>
       </c>
@@ -10974,26 +10075,21 @@
       <c r="E40" s="8">
         <v>8.9489291724392004</v>
       </c>
-      <c r="G40" s="1">
+      <c r="F40" s="1">
         <v>275.5</v>
       </c>
-      <c r="H40" s="8">
+      <c r="G40" s="8">
         <v>767.38704148583633</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I40" s="1">
         <v>8.9489291724392004</v>
       </c>
-      <c r="J40" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K40" s="1">
-        <v>275.5</v>
-      </c>
-      <c r="L40" s="8">
-        <v>767.38704148583633</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>296</v>
       </c>
@@ -11009,26 +10105,21 @@
       <c r="E41" s="8">
         <v>6.6395280956806966</v>
       </c>
-      <c r="G41" s="1">
+      <c r="F41" s="1">
         <v>277.5</v>
       </c>
-      <c r="H41" s="8">
+      <c r="G41" s="8">
         <v>754.43717152141676</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I41" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J41" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K41" s="1">
-        <v>277.5</v>
-      </c>
-      <c r="L41" s="8">
-        <v>754.43717152141676</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>299</v>
       </c>
@@ -11044,26 +10135,21 @@
       <c r="E42" s="8">
         <v>9.2376043070340135</v>
       </c>
-      <c r="G42" s="1">
+      <c r="F42" s="1">
         <v>280.5</v>
       </c>
-      <c r="H42" s="8">
+      <c r="G42" s="8">
         <v>729.87584121464397</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I42" s="1">
         <v>9.2376043070340135</v>
       </c>
-      <c r="J42" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K42" s="1">
-        <v>280.5</v>
-      </c>
-      <c r="L42" s="8">
-        <v>729.87584121464397</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>300</v>
       </c>
@@ -11079,26 +10165,21 @@
       <c r="E43" s="8">
         <v>9.5262794416288248</v>
       </c>
-      <c r="G43" s="1">
+      <c r="F43" s="1">
         <v>281.5</v>
       </c>
-      <c r="H43" s="8">
+      <c r="G43" s="8">
         <v>725.36750970623939</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I43" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J43" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K43" s="1">
-        <v>281.5</v>
-      </c>
-      <c r="L43" s="8">
-        <v>725.36750970623939</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>301</v>
       </c>
@@ -11114,26 +10195,21 @@
       <c r="E44" s="8">
         <v>9.2376043070340135</v>
       </c>
-      <c r="G44" s="1">
+      <c r="F44" s="1">
         <v>282.5</v>
       </c>
-      <c r="H44" s="8">
+      <c r="G44" s="8">
         <v>717.87462501523669</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I44" s="1">
         <v>9.2376043070340135</v>
       </c>
-      <c r="J44" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K44" s="1">
-        <v>282.5</v>
-      </c>
-      <c r="L44" s="8">
-        <v>717.87462501523669</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>302</v>
       </c>
@@ -11149,26 +10225,21 @@
       <c r="E45" s="8">
         <v>5.4848275573014451</v>
       </c>
-      <c r="G45" s="1">
+      <c r="F45" s="1">
         <v>283.5</v>
       </c>
-      <c r="H45" s="8">
+      <c r="G45" s="8">
         <v>706.45534290239664</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I45" s="1">
         <v>5.4848275573014451</v>
       </c>
-      <c r="J45" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K45" s="1">
-        <v>283.5</v>
-      </c>
-      <c r="L45" s="8">
-        <v>706.45534290239664</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>303</v>
       </c>
@@ -11184,26 +10255,21 @@
       <c r="E46" s="8">
         <v>6.6395280956806966</v>
       </c>
-      <c r="G46" s="1">
+      <c r="F46" s="1">
         <v>284.5</v>
       </c>
-      <c r="H46" s="8">
+      <c r="G46" s="8">
         <v>698.43410346668998</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I46" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J46" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K46" s="1">
-        <v>284.5</v>
-      </c>
-      <c r="L46" s="8">
-        <v>698.43410346668998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>304</v>
       </c>
@@ -11219,26 +10285,21 @@
       <c r="E47" s="8">
         <v>6.6395280956806966</v>
       </c>
-      <c r="G47" s="1">
+      <c r="F47" s="1">
         <v>285.5</v>
       </c>
-      <c r="H47" s="8">
+      <c r="G47" s="8">
         <v>697.43410346668998</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I47" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J47" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K47" s="1">
-        <v>285.5</v>
-      </c>
-      <c r="L47" s="8">
-        <v>697.43410346668998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>305</v>
       </c>
@@ -11254,26 +10315,21 @@
       <c r="E48" s="8">
         <v>5.7735026918962582</v>
       </c>
-      <c r="G48" s="1">
+      <c r="F48" s="1">
         <v>286.5</v>
       </c>
-      <c r="H48" s="8">
+      <c r="G48" s="8">
         <v>688.94979793160257</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I48" s="1">
         <v>5.7735026918962582</v>
       </c>
-      <c r="J48" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K48" s="1">
-        <v>286.5</v>
-      </c>
-      <c r="L48" s="8">
-        <v>688.94979793160257</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>306</v>
       </c>
@@ -11289,26 +10345,21 @@
       <c r="E49" s="8">
         <v>4.3301270189221936</v>
       </c>
-      <c r="G49" s="1">
+      <c r="F49" s="1">
         <v>287.5</v>
       </c>
-      <c r="H49" s="8">
+      <c r="G49" s="8">
         <v>684.47166206396048</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I49" s="1">
         <v>4.3301270189221936</v>
       </c>
-      <c r="J49" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K49" s="1">
-        <v>287.5</v>
-      </c>
-      <c r="L49" s="8">
-        <v>684.47166206396048</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>307</v>
       </c>
@@ -11324,26 +10375,21 @@
       <c r="E50" s="8">
         <v>5.196152422706632</v>
       </c>
-      <c r="G50" s="1">
+      <c r="F50" s="1">
         <v>288.5</v>
       </c>
-      <c r="H50" s="8">
+      <c r="G50" s="8">
         <v>680.95909006382692</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I50" s="1">
         <v>5.196152422706632</v>
       </c>
-      <c r="J50" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K50" s="1">
-        <v>288.5</v>
-      </c>
-      <c r="L50" s="8">
-        <v>680.95909006382692</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>308</v>
       </c>
@@ -11359,26 +10405,21 @@
       <c r="E51" s="8">
         <v>4.9074772881118189</v>
       </c>
-      <c r="G51" s="1">
+      <c r="F51" s="1">
         <v>289.5</v>
       </c>
-      <c r="H51" s="8">
+      <c r="G51" s="8">
         <v>673.46326825153972</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I51" s="1">
         <v>4.9074772881118189</v>
       </c>
-      <c r="J51" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K51" s="1">
-        <v>289.5</v>
-      </c>
-      <c r="L51" s="8">
-        <v>673.46326825153972</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>309</v>
       </c>
@@ -11394,26 +10435,21 @@
       <c r="E52" s="8">
         <v>4.9074772881118189</v>
       </c>
-      <c r="G52" s="1">
+      <c r="F52" s="1">
         <v>290.5</v>
       </c>
-      <c r="H52" s="8">
+      <c r="G52" s="8">
         <v>668.46311824386737</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I52" s="1">
         <v>4.9074772881118189</v>
       </c>
-      <c r="J52" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K52" s="1">
-        <v>290.5</v>
-      </c>
-      <c r="L52" s="8">
-        <v>668.46311824386737</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>310</v>
       </c>
@@ -11429,26 +10465,21 @@
       <c r="E53" s="8">
         <v>5.4848275573014451</v>
       </c>
-      <c r="G53" s="1">
+      <c r="F53" s="1">
         <v>291.5</v>
       </c>
-      <c r="H53" s="8">
+      <c r="G53" s="8">
         <v>665.45383522701468</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I53" s="1">
         <v>5.4848275573014451</v>
       </c>
-      <c r="J53" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K53" s="1">
-        <v>291.5</v>
-      </c>
-      <c r="L53" s="8">
-        <v>665.45383522701468</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>311</v>
       </c>
@@ -11464,26 +10495,21 @@
       <c r="E54" s="8">
         <v>2.598076211353316</v>
       </c>
-      <c r="G54" s="1">
+      <c r="F54" s="1">
         <v>292.5</v>
       </c>
-      <c r="H54" s="8">
+      <c r="G54" s="8">
         <v>656.48955641615851</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I54" s="1">
         <v>2.598076211353316</v>
       </c>
-      <c r="J54" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K54" s="1">
-        <v>292.5</v>
-      </c>
-      <c r="L54" s="8">
-        <v>656.48955641615851</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>312</v>
       </c>
@@ -11499,26 +10525,21 @@
       <c r="E55" s="8">
         <v>4.6188021535170067</v>
       </c>
-      <c r="G55" s="1">
+      <c r="F55" s="1">
         <v>293.5</v>
       </c>
-      <c r="H55" s="8">
+      <c r="G55" s="8">
         <v>653.96694158426715</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I55" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J55" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K55" s="1">
-        <v>293.5</v>
-      </c>
-      <c r="L55" s="8">
-        <v>653.96694158426715</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>313</v>
       </c>
@@ -11534,26 +10555,21 @@
       <c r="E56" s="8">
         <v>3.4641016151377548</v>
       </c>
-      <c r="G56" s="1">
+      <c r="F56" s="1">
         <v>294.5</v>
       </c>
-      <c r="H56" s="8">
+      <c r="G56" s="8">
         <v>647.98130822981193</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I56" s="1">
         <v>3.4641016151377548</v>
       </c>
-      <c r="J56" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K56" s="1">
-        <v>294.5</v>
-      </c>
-      <c r="L56" s="8">
-        <v>647.98130822981193</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>314</v>
       </c>
@@ -11569,26 +10585,21 @@
       <c r="E57" s="8">
         <v>3.4641016151377548</v>
       </c>
-      <c r="G57" s="1">
+      <c r="F57" s="1">
         <v>295.5</v>
       </c>
-      <c r="H57" s="8">
+      <c r="G57" s="8">
         <v>644.98126932838807</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I57" s="1">
         <v>3.4641016151377548</v>
       </c>
-      <c r="J57" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K57" s="1">
-        <v>295.5</v>
-      </c>
-      <c r="L57" s="8">
-        <v>644.98126932838807</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>316</v>
       </c>
@@ -11604,26 +10615,21 @@
       <c r="E58" s="8">
         <v>4.6188021535170067</v>
       </c>
-      <c r="G58" s="1">
+      <c r="F58" s="1">
         <v>297.5</v>
       </c>
-      <c r="H58" s="8">
+      <c r="G58" s="8">
         <v>634.9664212342426</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I58" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J58" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K58" s="1">
-        <v>297.5</v>
-      </c>
-      <c r="L58" s="8">
-        <v>634.9664212342426</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>318</v>
       </c>
@@ -11639,26 +10645,21 @@
       <c r="E59" s="8">
         <v>3.7527767497325675</v>
       </c>
-      <c r="G59" s="1">
+      <c r="F59" s="1">
         <v>299.5</v>
       </c>
-      <c r="H59" s="8">
+      <c r="G59" s="8">
         <v>626.47768066658602</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I59" s="1">
         <v>3.7527767497325675</v>
       </c>
-      <c r="J59" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K59" s="1">
-        <v>299.5</v>
-      </c>
-      <c r="L59" s="8">
-        <v>626.47768066658602</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>320</v>
       </c>
@@ -11674,26 +10675,21 @@
       <c r="E60" s="8">
         <v>4.6188021535170067</v>
       </c>
-      <c r="G60" s="1">
+      <c r="F60" s="1">
         <v>301.5</v>
       </c>
-      <c r="H60" s="8">
+      <c r="G60" s="8">
         <v>614.96584783011167</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I60" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J60" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K60" s="1">
-        <v>301.5</v>
-      </c>
-      <c r="L60" s="8">
-        <v>614.96584783011167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>325</v>
       </c>
@@ -11709,26 +10705,21 @@
       <c r="E61" s="8">
         <v>4.0414518843273806</v>
       </c>
-      <c r="G61" s="1">
+      <c r="F61" s="1">
         <v>306.5</v>
       </c>
-      <c r="H61" s="8">
+      <c r="G61" s="8">
         <v>595.97345573965447</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I61" s="1">
         <v>4.0414518843273806</v>
       </c>
-      <c r="J61" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K61" s="1">
-        <v>306.5</v>
-      </c>
-      <c r="L61" s="8">
-        <v>595.97345573965447</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>330</v>
       </c>
@@ -11744,26 +10735,21 @@
       <c r="E62" s="8">
         <v>2.598076211353316</v>
       </c>
-      <c r="G62" s="1">
+      <c r="F62" s="1">
         <v>311.5</v>
       </c>
-      <c r="H62" s="8">
+      <c r="G62" s="8">
         <v>578.48887966849986</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I62" s="1">
         <v>2.598076211353316</v>
       </c>
-      <c r="J62" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K62" s="1">
-        <v>311.5</v>
-      </c>
-      <c r="L62" s="8">
-        <v>578.48887966849986</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>335</v>
       </c>
@@ -11776,27 +10762,21 @@
       <c r="E63" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="1">
+      <c r="F63" s="1">
         <v>316.5</v>
       </c>
-      <c r="H63" s="8">
+      <c r="G63" s="8">
         <v>549</v>
       </c>
+      <c r="H63" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I63" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J63" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K63" s="1">
-        <v>316.5</v>
-      </c>
-      <c r="L63" s="8">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>340</v>
       </c>
@@ -11809,27 +10789,21 @@
       <c r="E64" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F64" s="9"/>
-      <c r="G64" s="1">
+      <c r="F64" s="1">
         <v>321.5</v>
       </c>
-      <c r="H64" s="8">
+      <c r="G64" s="8">
         <v>529</v>
       </c>
+      <c r="H64" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I64" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J64" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K64" s="1">
-        <v>321.5</v>
-      </c>
-      <c r="L64" s="8">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>345</v>
       </c>
@@ -11842,27 +10816,21 @@
       <c r="E65" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F65" s="9"/>
-      <c r="G65" s="1">
+      <c r="F65" s="1">
         <v>326.5</v>
       </c>
-      <c r="H65" s="8">
+      <c r="G65" s="8">
         <v>523</v>
       </c>
+      <c r="H65" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I65" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J65" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K65" s="1">
-        <v>326.5</v>
-      </c>
-      <c r="L65" s="8">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>350</v>
       </c>
@@ -11875,27 +10843,21 @@
       <c r="E66" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F66" s="9"/>
-      <c r="G66" s="1">
+      <c r="F66" s="1">
         <v>331.5</v>
       </c>
-      <c r="H66" s="8">
+      <c r="G66" s="8">
         <v>512</v>
       </c>
+      <c r="H66" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I66" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J66" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K66" s="1">
-        <v>331.5</v>
-      </c>
-      <c r="L66" s="8">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>355</v>
       </c>
@@ -11908,27 +10870,21 @@
       <c r="E67" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F67" s="9"/>
-      <c r="G67" s="1">
+      <c r="F67" s="1">
         <v>336.5</v>
       </c>
-      <c r="H67" s="8">
+      <c r="G67" s="8">
         <v>499</v>
       </c>
+      <c r="H67" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I67" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J67" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K67" s="1">
-        <v>336.5</v>
-      </c>
-      <c r="L67" s="8">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>360</v>
       </c>
@@ -11941,27 +10897,21 @@
       <c r="E68" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F68" s="9"/>
-      <c r="G68" s="1">
+      <c r="F68" s="1">
         <v>341.5</v>
       </c>
-      <c r="H68" s="8">
+      <c r="G68" s="8">
         <v>489</v>
       </c>
+      <c r="H68" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I68" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J68" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K68" s="1">
-        <v>341.5</v>
-      </c>
-      <c r="L68" s="8">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>365</v>
       </c>
@@ -11974,27 +10924,21 @@
       <c r="E69" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F69" s="9"/>
-      <c r="G69" s="1">
+      <c r="F69" s="1">
         <v>346.5</v>
       </c>
-      <c r="H69" s="8">
+      <c r="G69" s="8">
         <v>479</v>
       </c>
+      <c r="H69" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I69" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J69" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K69" s="1">
-        <v>346.5</v>
-      </c>
-      <c r="L69" s="8">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>370</v>
       </c>
@@ -12007,27 +10951,21 @@
       <c r="E70" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F70" s="9"/>
-      <c r="G70" s="1">
+      <c r="F70" s="1">
         <v>351.5</v>
       </c>
-      <c r="H70" s="8">
+      <c r="G70" s="8">
         <v>468</v>
       </c>
+      <c r="H70" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I70" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J70" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K70" s="1">
-        <v>351.5</v>
-      </c>
-      <c r="L70" s="8">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>375</v>
       </c>
@@ -12040,27 +10978,21 @@
       <c r="E71" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F71" s="9"/>
-      <c r="G71" s="1">
+      <c r="F71" s="1">
         <v>356.5</v>
       </c>
-      <c r="H71" s="8">
+      <c r="G71" s="8">
         <v>458</v>
       </c>
+      <c r="H71" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I71" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J71" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K71" s="1">
-        <v>356.5</v>
-      </c>
-      <c r="L71" s="8">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>380</v>
       </c>
@@ -12073,27 +11005,21 @@
       <c r="E72" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F72" s="9"/>
-      <c r="G72" s="1">
+      <c r="F72" s="1">
         <v>361.5</v>
       </c>
-      <c r="H72" s="8">
+      <c r="G72" s="8">
         <v>451</v>
       </c>
+      <c r="H72" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I72" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J72" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K72" s="1">
-        <v>361.5</v>
-      </c>
-      <c r="L72" s="8">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>385</v>
       </c>
@@ -12106,27 +11032,21 @@
       <c r="E73" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F73" s="9"/>
-      <c r="G73" s="1">
+      <c r="F73" s="1">
         <v>366.5</v>
       </c>
-      <c r="H73" s="8">
+      <c r="G73" s="8">
         <v>445</v>
       </c>
+      <c r="H73" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I73" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J73" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K73" s="1">
-        <v>366.5</v>
-      </c>
-      <c r="L73" s="8">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>390</v>
       </c>
@@ -12139,27 +11059,21 @@
       <c r="E74" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F74" s="9"/>
-      <c r="G74" s="1">
+      <c r="F74" s="1">
         <v>371.5</v>
       </c>
-      <c r="H74" s="8">
+      <c r="G74" s="8">
         <v>436</v>
       </c>
+      <c r="H74" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I74" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J74" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K74" s="1">
-        <v>371.5</v>
-      </c>
-      <c r="L74" s="8">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>395</v>
       </c>
@@ -12172,27 +11086,21 @@
       <c r="E75" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F75" s="9"/>
-      <c r="G75" s="1">
+      <c r="F75" s="1">
         <v>376.5</v>
       </c>
-      <c r="H75" s="8">
+      <c r="G75" s="8">
         <v>428</v>
       </c>
+      <c r="H75" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I75" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J75" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K75" s="1">
-        <v>376.5</v>
-      </c>
-      <c r="L75" s="8">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>400</v>
       </c>
@@ -12205,27 +11113,21 @@
       <c r="E76" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F76" s="9"/>
-      <c r="G76" s="1">
+      <c r="F76" s="1">
         <v>381.5</v>
       </c>
-      <c r="H76" s="8">
+      <c r="G76" s="8">
         <v>420</v>
       </c>
+      <c r="H76" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I76" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J76" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K76" s="1">
-        <v>381.5</v>
-      </c>
-      <c r="L76" s="8">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>405</v>
       </c>
@@ -12238,27 +11140,21 @@
       <c r="E77" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F77" s="9"/>
-      <c r="G77" s="1">
+      <c r="F77" s="1">
         <v>386.5</v>
       </c>
-      <c r="H77" s="8">
+      <c r="G77" s="8">
         <v>413</v>
       </c>
+      <c r="H77" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I77" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J77" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K77" s="1">
-        <v>386.5</v>
-      </c>
-      <c r="L77" s="8">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>410</v>
       </c>
@@ -12271,27 +11167,21 @@
       <c r="E78" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F78" s="9"/>
-      <c r="G78" s="1">
+      <c r="F78" s="1">
         <v>391.5</v>
       </c>
-      <c r="H78" s="8">
+      <c r="G78" s="8">
         <v>404</v>
       </c>
+      <c r="H78" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I78" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J78" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K78" s="1">
-        <v>391.5</v>
-      </c>
-      <c r="L78" s="8">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>415</v>
       </c>
@@ -12304,28 +11194,20 @@
       <c r="E79" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F79" s="9"/>
-      <c r="G79" s="1">
+      <c r="F79" s="1">
         <v>396.5</v>
       </c>
-      <c r="H79" s="8">
+      <c r="G79" s="8">
         <v>397</v>
       </c>
+      <c r="H79" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I79" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J79" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K79" s="1">
-        <v>396.5</v>
-      </c>
-      <c r="L79" s="1">
-        <f>H79-1</f>
-        <v>396</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>420</v>
       </c>
@@ -12338,28 +11220,20 @@
       <c r="E80" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F80" s="9"/>
-      <c r="G80" s="1">
+      <c r="F80" s="1">
         <v>401.5</v>
       </c>
-      <c r="H80" s="8">
+      <c r="G80" s="8">
         <v>400</v>
       </c>
+      <c r="H80" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I80" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J80" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K80" s="1">
-        <v>401.5</v>
-      </c>
-      <c r="L80" s="1">
-        <f>H80-7</f>
-        <v>393</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>425</v>
       </c>
@@ -12372,28 +11246,20 @@
       <c r="E81" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F81" s="9"/>
-      <c r="G81" s="1">
+      <c r="F81" s="1">
         <v>406.5</v>
       </c>
-      <c r="H81" s="8">
+      <c r="G81" s="8">
         <v>398</v>
       </c>
+      <c r="H81" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I81" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J81" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K81" s="1">
-        <v>406.5</v>
-      </c>
-      <c r="L81" s="1">
-        <f t="shared" ref="L81:L117" si="0">H81-7</f>
-        <v>391</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>430</v>
       </c>
@@ -12406,28 +11272,20 @@
       <c r="E82" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F82" s="9"/>
-      <c r="G82" s="1">
+      <c r="F82" s="1">
         <v>411.5</v>
       </c>
-      <c r="H82" s="8">
+      <c r="G82" s="8">
         <v>395</v>
       </c>
+      <c r="H82" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I82" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J82" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K82" s="1">
-        <v>411.5</v>
-      </c>
-      <c r="L82" s="1">
-        <f t="shared" si="0"/>
-        <v>388</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>435</v>
       </c>
@@ -12440,28 +11298,20 @@
       <c r="E83" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F83" s="9"/>
-      <c r="G83" s="1">
+      <c r="F83" s="1">
         <v>416.5</v>
       </c>
-      <c r="H83" s="8">
+      <c r="G83" s="8">
         <v>390</v>
       </c>
+      <c r="H83" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I83" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J83" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K83" s="1">
-        <v>416.5</v>
-      </c>
-      <c r="L83" s="1">
-        <f t="shared" si="0"/>
-        <v>383</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>440</v>
       </c>
@@ -12474,28 +11324,20 @@
       <c r="E84" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F84" s="9"/>
-      <c r="G84" s="1">
+      <c r="F84" s="1">
         <v>421.5</v>
       </c>
-      <c r="H84" s="8">
+      <c r="G84" s="8">
         <v>387</v>
       </c>
+      <c r="H84" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I84" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J84" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K84" s="1">
-        <v>421.5</v>
-      </c>
-      <c r="L84" s="1">
-        <f t="shared" si="0"/>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>445</v>
       </c>
@@ -12508,28 +11350,20 @@
       <c r="E85" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F85" s="9"/>
-      <c r="G85" s="1">
+      <c r="F85" s="1">
         <v>426.5</v>
       </c>
-      <c r="H85" s="8">
+      <c r="G85" s="8">
         <v>383</v>
       </c>
+      <c r="H85" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I85" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J85" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K85" s="1">
-        <v>426.5</v>
-      </c>
-      <c r="L85" s="1">
-        <f t="shared" si="0"/>
-        <v>376</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>450</v>
       </c>
@@ -12542,28 +11376,20 @@
       <c r="E86" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F86" s="9"/>
-      <c r="G86" s="1">
+      <c r="F86" s="1">
         <v>431.5</v>
       </c>
-      <c r="H86" s="8">
+      <c r="G86" s="8">
         <v>379</v>
       </c>
+      <c r="H86" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I86" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J86" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K86" s="1">
-        <v>431.5</v>
-      </c>
-      <c r="L86" s="1">
-        <f t="shared" si="0"/>
-        <v>372</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>460</v>
       </c>
@@ -12576,28 +11402,20 @@
       <c r="E87" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F87" s="9"/>
-      <c r="G87" s="1">
+      <c r="F87" s="1">
         <v>441.5</v>
       </c>
-      <c r="H87" s="8">
+      <c r="G87" s="8">
         <v>370</v>
       </c>
+      <c r="H87" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I87" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J87" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K87" s="1">
-        <v>441.5</v>
-      </c>
-      <c r="L87" s="1">
-        <f t="shared" si="0"/>
-        <v>363</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>470</v>
       </c>
@@ -12610,28 +11428,20 @@
       <c r="E88" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F88" s="9"/>
-      <c r="G88" s="1">
+      <c r="F88" s="1">
         <v>451.5</v>
       </c>
-      <c r="H88" s="8">
+      <c r="G88" s="8">
         <v>365</v>
       </c>
+      <c r="H88" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I88" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J88" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K88" s="1">
-        <v>451.5</v>
-      </c>
-      <c r="L88" s="1">
-        <f t="shared" si="0"/>
-        <v>358</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>480</v>
       </c>
@@ -12644,28 +11454,20 @@
       <c r="E89" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F89" s="9"/>
-      <c r="G89" s="1">
+      <c r="F89" s="1">
         <v>461.5</v>
       </c>
-      <c r="H89" s="8">
+      <c r="G89" s="8">
         <v>358</v>
       </c>
+      <c r="H89" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I89" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J89" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K89" s="1">
-        <v>461.5</v>
-      </c>
-      <c r="L89" s="1">
-        <f t="shared" si="0"/>
-        <v>351</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>490</v>
       </c>
@@ -12678,28 +11480,20 @@
       <c r="E90" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F90" s="9"/>
-      <c r="G90" s="1">
+      <c r="F90" s="1">
         <v>471.5</v>
       </c>
-      <c r="H90" s="8">
+      <c r="G90" s="8">
         <v>343</v>
       </c>
+      <c r="H90" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I90" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J90" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K90" s="1">
-        <v>471.5</v>
-      </c>
-      <c r="L90" s="1">
-        <f t="shared" si="0"/>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>500</v>
       </c>
@@ -12712,28 +11506,20 @@
       <c r="E91" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F91" s="9"/>
-      <c r="G91" s="1">
+      <c r="F91" s="1">
         <v>481.5</v>
       </c>
-      <c r="H91" s="8">
+      <c r="G91" s="8">
         <v>348</v>
       </c>
+      <c r="H91" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I91" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J91" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K91" s="1">
-        <v>481.5</v>
-      </c>
-      <c r="L91" s="1">
-        <f t="shared" si="0"/>
-        <v>341</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>510</v>
       </c>
@@ -12746,28 +11532,20 @@
       <c r="E92" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F92" s="9"/>
-      <c r="G92" s="1">
+      <c r="F92" s="1">
         <v>491.5</v>
       </c>
-      <c r="H92" s="8">
+      <c r="G92" s="8">
         <v>343</v>
       </c>
+      <c r="H92" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I92" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J92" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K92" s="1">
-        <v>491.5</v>
-      </c>
-      <c r="L92" s="1">
-        <f t="shared" si="0"/>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>520</v>
       </c>
@@ -12780,28 +11558,20 @@
       <c r="E93" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F93" s="9"/>
-      <c r="G93" s="1">
+      <c r="F93" s="1">
         <v>501.5</v>
       </c>
-      <c r="H93" s="8">
+      <c r="G93" s="8">
         <v>338</v>
       </c>
+      <c r="H93" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I93" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J93" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K93" s="1">
-        <v>501.5</v>
-      </c>
-      <c r="L93" s="1">
-        <f t="shared" si="0"/>
-        <v>331</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>530</v>
       </c>
@@ -12814,28 +11584,20 @@
       <c r="E94" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F94" s="9"/>
-      <c r="G94" s="1">
+      <c r="F94" s="1">
         <v>511.5</v>
       </c>
-      <c r="H94" s="8">
+      <c r="G94" s="8">
         <v>333</v>
       </c>
+      <c r="H94" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I94" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J94" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K94" s="1">
-        <v>511.5</v>
-      </c>
-      <c r="L94" s="1">
-        <f t="shared" si="0"/>
-        <v>326</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>540</v>
       </c>
@@ -12848,28 +11610,20 @@
       <c r="E95" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F95" s="9"/>
-      <c r="G95" s="1">
+      <c r="F95" s="1">
         <v>521.5</v>
       </c>
-      <c r="H95" s="8">
+      <c r="G95" s="8">
         <v>328</v>
       </c>
+      <c r="H95" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I95" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J95" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K95" s="1">
-        <v>521.5</v>
-      </c>
-      <c r="L95" s="1">
-        <f t="shared" si="0"/>
-        <v>321</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>550</v>
       </c>
@@ -12882,28 +11636,20 @@
       <c r="E96" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F96" s="9"/>
-      <c r="G96" s="1">
+      <c r="F96" s="1">
         <v>531.5</v>
       </c>
-      <c r="H96" s="8">
+      <c r="G96" s="8">
         <v>323</v>
       </c>
+      <c r="H96" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I96" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J96" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K96" s="1">
-        <v>531.5</v>
-      </c>
-      <c r="L96" s="1">
-        <f t="shared" si="0"/>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>560</v>
       </c>
@@ -12916,28 +11662,20 @@
       <c r="E97" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F97" s="9"/>
-      <c r="G97" s="1">
+      <c r="F97" s="1">
         <v>541.5</v>
       </c>
-      <c r="H97" s="8">
+      <c r="G97" s="8">
         <v>323</v>
       </c>
+      <c r="H97" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I97" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J97" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K97" s="1">
-        <v>541.5</v>
-      </c>
-      <c r="L97" s="1">
-        <f t="shared" si="0"/>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>570</v>
       </c>
@@ -12950,28 +11688,20 @@
       <c r="E98" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F98" s="9"/>
-      <c r="G98" s="1">
+      <c r="F98" s="1">
         <v>551.5</v>
       </c>
-      <c r="H98" s="8">
+      <c r="G98" s="8">
         <v>318</v>
       </c>
+      <c r="H98" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I98" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J98" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K98" s="1">
-        <v>551.5</v>
-      </c>
-      <c r="L98" s="1">
-        <f t="shared" si="0"/>
-        <v>311</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>580</v>
       </c>
@@ -12984,28 +11714,20 @@
       <c r="E99" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F99" s="9"/>
-      <c r="G99" s="1">
+      <c r="F99" s="1">
         <v>561.5</v>
       </c>
-      <c r="H99" s="8">
+      <c r="G99" s="8">
         <v>315</v>
       </c>
+      <c r="H99" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I99" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J99" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K99" s="1">
-        <v>561.5</v>
-      </c>
-      <c r="L99" s="1">
-        <f t="shared" si="0"/>
-        <v>308</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>590</v>
       </c>
@@ -13018,28 +11740,20 @@
       <c r="E100" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F100" s="9"/>
-      <c r="G100" s="1">
+      <c r="F100" s="1">
         <v>571.5</v>
       </c>
-      <c r="H100" s="8">
+      <c r="G100" s="8">
         <v>313</v>
       </c>
+      <c r="H100" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I100" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J100" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K100" s="1">
-        <v>571.5</v>
-      </c>
-      <c r="L100" s="1">
-        <f t="shared" si="0"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>600</v>
       </c>
@@ -13052,28 +11766,20 @@
       <c r="E101" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F101" s="9"/>
-      <c r="G101" s="1">
+      <c r="F101" s="1">
         <v>581.5</v>
       </c>
-      <c r="H101" s="8">
+      <c r="G101" s="8">
         <v>308</v>
       </c>
+      <c r="H101" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I101" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J101" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K101" s="1">
-        <v>581.5</v>
-      </c>
-      <c r="L101" s="1">
-        <f t="shared" si="0"/>
-        <v>301</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>620</v>
       </c>
@@ -13086,28 +11792,20 @@
       <c r="E102" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F102" s="9"/>
-      <c r="G102" s="1">
+      <c r="F102" s="1">
         <v>601.5</v>
       </c>
-      <c r="H102" s="8">
+      <c r="G102" s="8">
         <v>303</v>
       </c>
+      <c r="H102" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I102" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J102" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K102" s="1">
-        <v>601.5</v>
-      </c>
-      <c r="L102" s="1">
-        <f t="shared" si="0"/>
-        <v>296</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>640</v>
       </c>
@@ -13120,28 +11818,20 @@
       <c r="E103" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F103" s="9"/>
-      <c r="G103" s="1">
+      <c r="F103" s="1">
         <v>621.5</v>
       </c>
-      <c r="H103" s="8">
+      <c r="G103" s="8">
         <v>297</v>
       </c>
+      <c r="H103" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I103" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J103" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K103" s="1">
-        <v>621.5</v>
-      </c>
-      <c r="L103" s="1">
-        <f t="shared" si="0"/>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>660</v>
       </c>
@@ -13154,28 +11844,20 @@
       <c r="E104" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F104" s="9"/>
-      <c r="G104" s="1">
+      <c r="F104" s="1">
         <v>641.5</v>
       </c>
-      <c r="H104" s="8">
+      <c r="G104" s="8">
         <v>296</v>
       </c>
+      <c r="H104" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I104" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J104" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K104" s="1">
-        <v>641.5</v>
-      </c>
-      <c r="L104" s="1">
-        <f t="shared" si="0"/>
-        <v>289</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>680</v>
       </c>
@@ -13188,28 +11870,20 @@
       <c r="E105" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F105" s="9"/>
-      <c r="G105" s="1">
+      <c r="F105" s="1">
         <v>661.5</v>
       </c>
-      <c r="H105" s="8">
+      <c r="G105" s="8">
         <v>290</v>
       </c>
+      <c r="H105" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I105" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J105" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K105" s="1">
-        <v>661.5</v>
-      </c>
-      <c r="L105" s="1">
-        <f t="shared" si="0"/>
-        <v>283</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>700</v>
       </c>
@@ -13222,28 +11896,20 @@
       <c r="E106" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F106" s="9"/>
-      <c r="G106" s="1">
+      <c r="F106" s="1">
         <v>681.5</v>
       </c>
-      <c r="H106" s="8">
+      <c r="G106" s="8">
         <v>288</v>
       </c>
+      <c r="H106" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I106" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J106" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K106" s="1">
-        <v>681.5</v>
-      </c>
-      <c r="L106" s="1">
-        <f t="shared" si="0"/>
-        <v>281</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>750</v>
       </c>
@@ -13256,28 +11922,20 @@
       <c r="E107" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F107" s="9"/>
-      <c r="G107" s="1">
+      <c r="F107" s="1">
         <v>731.5</v>
       </c>
-      <c r="H107" s="8">
+      <c r="G107" s="8">
         <v>278</v>
       </c>
+      <c r="H107" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I107" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J107" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K107" s="1">
-        <v>731.5</v>
-      </c>
-      <c r="L107" s="1">
-        <f t="shared" si="0"/>
-        <v>271</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>800</v>
       </c>
@@ -13290,28 +11948,20 @@
       <c r="E108" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F108" s="9"/>
-      <c r="G108" s="1">
+      <c r="F108" s="1">
         <v>781.5</v>
       </c>
-      <c r="H108" s="8">
+      <c r="G108" s="8">
         <v>271</v>
       </c>
+      <c r="H108" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I108" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J108" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K108" s="1">
-        <v>781.5</v>
-      </c>
-      <c r="L108" s="1">
-        <f t="shared" si="0"/>
-        <v>264</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>850</v>
       </c>
@@ -13324,28 +11974,20 @@
       <c r="E109" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F109" s="9"/>
-      <c r="G109" s="1">
+      <c r="F109" s="1">
         <v>831.5</v>
       </c>
-      <c r="H109" s="8">
+      <c r="G109" s="8">
         <v>266</v>
       </c>
+      <c r="H109" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I109" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J109" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K109" s="1">
-        <v>831.5</v>
-      </c>
-      <c r="L109" s="1">
-        <f t="shared" si="0"/>
-        <v>259</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>900</v>
       </c>
@@ -13358,28 +12000,20 @@
       <c r="E110" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F110" s="9"/>
-      <c r="G110" s="1">
+      <c r="F110" s="1">
         <v>881.5</v>
       </c>
-      <c r="H110" s="8">
+      <c r="G110" s="8">
         <v>262</v>
       </c>
+      <c r="H110" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I110" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J110" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K110" s="1">
-        <v>881.5</v>
-      </c>
-      <c r="L110" s="1">
-        <f t="shared" si="0"/>
-        <v>255</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>1000</v>
       </c>
@@ -13392,28 +12026,20 @@
       <c r="E111" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F111" s="9"/>
-      <c r="G111" s="1">
+      <c r="F111" s="1">
         <v>981.5</v>
       </c>
-      <c r="H111" s="8">
+      <c r="G111" s="8">
         <v>253</v>
       </c>
+      <c r="H111" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I111" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J111" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K111" s="1">
-        <v>981.5</v>
-      </c>
-      <c r="L111" s="1">
-        <f t="shared" si="0"/>
-        <v>246</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>1100</v>
       </c>
@@ -13426,28 +12052,20 @@
       <c r="E112" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F112" s="9"/>
-      <c r="G112" s="1">
+      <c r="F112" s="1">
         <v>1081.5</v>
       </c>
-      <c r="H112" s="8">
+      <c r="G112" s="8">
         <v>247</v>
       </c>
+      <c r="H112" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I112" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J112" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K112" s="1">
-        <v>1081.5</v>
-      </c>
-      <c r="L112" s="1">
-        <f t="shared" si="0"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>1200</v>
       </c>
@@ -13460,28 +12078,20 @@
       <c r="E113" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F113" s="9"/>
-      <c r="G113" s="1">
+      <c r="F113" s="1">
         <v>1181.5</v>
       </c>
-      <c r="H113" s="8">
+      <c r="G113" s="8">
         <v>243</v>
       </c>
+      <c r="H113" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I113" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J113" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K113" s="1">
-        <v>1181.5</v>
-      </c>
-      <c r="L113" s="1">
-        <f t="shared" si="0"/>
-        <v>236</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>1300</v>
       </c>
@@ -13494,28 +12104,20 @@
       <c r="E114" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F114" s="9"/>
-      <c r="G114" s="1">
+      <c r="F114" s="1">
         <v>1281.5</v>
       </c>
-      <c r="H114" s="8">
+      <c r="G114" s="8">
         <v>240</v>
       </c>
+      <c r="H114" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I114" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J114" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K114" s="1">
-        <v>1281.5</v>
-      </c>
-      <c r="L114" s="1">
-        <f t="shared" si="0"/>
-        <v>233</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>1400</v>
       </c>
@@ -13528,28 +12130,20 @@
       <c r="E115" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F115" s="9"/>
-      <c r="G115" s="1">
+      <c r="F115" s="1">
         <v>1381.5</v>
       </c>
-      <c r="H115" s="8">
+      <c r="G115" s="8">
         <v>236</v>
       </c>
+      <c r="H115" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I115" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J115" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K115" s="1">
-        <v>1381.5</v>
-      </c>
-      <c r="L115" s="1">
-        <f t="shared" si="0"/>
-        <v>229</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>1500</v>
       </c>
@@ -13562,28 +12156,20 @@
       <c r="E116" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F116" s="9"/>
-      <c r="G116" s="1">
+      <c r="F116" s="1">
         <v>1481.5</v>
       </c>
-      <c r="H116" s="8">
+      <c r="G116" s="8">
         <v>234</v>
       </c>
+      <c r="H116" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I116" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J116" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K116" s="1">
-        <v>1481.5</v>
-      </c>
-      <c r="L116" s="1">
-        <f t="shared" si="0"/>
-        <v>227</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>1650</v>
       </c>
@@ -13596,54 +12182,46 @@
       <c r="E117" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="F117" s="9"/>
-      <c r="G117" s="1">
+      <c r="F117" s="1">
         <v>1631.5</v>
       </c>
-      <c r="H117" s="8">
+      <c r="G117" s="8">
         <v>230</v>
       </c>
+      <c r="H117" s="1">
+        <v>0.11547005383792516</v>
+      </c>
       <c r="I117" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J117" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="K117" s="1">
-        <v>1631.5</v>
-      </c>
-      <c r="L117" s="1">
-        <f t="shared" si="0"/>
-        <v>223</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7"/>
     </row>
-    <row r="119" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7"/>
     </row>
-    <row r="120" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7"/>
     </row>
-    <row r="121" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7"/>
     </row>
-    <row r="122" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7"/>
     </row>
-    <row r="123" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7"/>
     </row>
-    <row r="124" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7"/>
     </row>
-    <row r="125" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7"/>
     </row>
-    <row r="126" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="129" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="130" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/Laboratorio/esperienza2/prove/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/prove/esperienza2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\Documents\UNIVERSITA'\III ANNO\Laboratorio-di-Ottica\Laboratorio\esperienza2\prove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C939CBC3-6977-412D-B250-39F1B618594F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD6459E-ED43-4A27-A1BA-86982DD69547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t xml:space="preserve"> L</t>
   </si>
@@ -2307,6 +2307,9 @@
               <c:f>Dati!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>p</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2343,8 +2346,356 @@
             <c:numRef>
               <c:f>Dati!$J$2:$J$130</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="129"/>
+                <c:pt idx="0">
+                  <c:v>232.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>233.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>234.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>235.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>236.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>237.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>238.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>239.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>240.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>241.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>242.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>243.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>245.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>246.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>247.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>249.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>250.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>251.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>252.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>253.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>254.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>255.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>256.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>257.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>258.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>259.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>260.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>261.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>262.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>263.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>264.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>265.5</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>267.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>269.5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>271.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>273.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>275.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>280.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>281.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>282.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>283.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>284.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>285.5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>286.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>287.5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>288.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>289.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>290.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>291.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>292.5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>293.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>294.5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>295.5</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>297.5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>299.5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>301.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>306.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>311.5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>316.5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>321.5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>326.5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>331.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>336.5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>341.5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>346.5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>351.5</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>356.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>361.5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>366.5</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>371.5</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>376.5</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>381.5</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>386.5</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>391.5</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>396.5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>401.5</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>401.5</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>406.5</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>411.5</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>416.5</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>421.5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>426.5</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>436.5</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>446.5</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>456.5</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>466.5</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>476.5</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>486.5</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>496.5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>506.5</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>516.5</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>526.5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>536.5</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>546.5</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>556.5</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>566.5</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>576.5</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>596.5</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>616.5</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>636.5</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>656.5</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>676.5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>726.5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>776.5</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>826.5</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>876.5</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>976.5</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1076.5</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1176.5</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1276.5</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1376.5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1476.5</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1626.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2449,6 +2800,1002 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="928514991"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dati!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>q</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Dati!$J$2:$J$130</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="129"/>
+                <c:pt idx="0">
+                  <c:v>232.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>233.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>234.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>235.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>236.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>237.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>238.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>239.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>240.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>241.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>242.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>243.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>245.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>246.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>247.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>249.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>250.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>251.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>252.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>253.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>254.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>255.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>256.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>257.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>258.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>259.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>260.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>261.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>262.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>263.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>264.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>265.5</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>267.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>269.5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>271.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>273.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>275.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>280.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>281.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>282.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>283.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>284.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>285.5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>286.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>287.5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>288.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>289.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>290.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>291.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>292.5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>293.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>294.5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>295.5</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>297.5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>299.5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>301.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>306.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>311.5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>316.5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>321.5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>326.5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>331.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>336.5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>341.5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>346.5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>351.5</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>356.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>361.5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>366.5</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>371.5</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>376.5</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>381.5</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>386.5</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>391.5</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>396.5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>401.5</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>401.5</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>406.5</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>411.5</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>416.5</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>421.5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>426.5</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>436.5</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>446.5</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>456.5</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>466.5</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>476.5</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>486.5</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>496.5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>506.5</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>516.5</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>526.5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>536.5</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>546.5</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>556.5</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>566.5</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>576.5</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>596.5</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>616.5</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>636.5</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>656.5</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>676.5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>726.5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>776.5</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>826.5</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>876.5</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>976.5</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1076.5</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1176.5</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1276.5</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1376.5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1476.5</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1626.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Dati!$K$2:$K$130</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="129"/>
+                <c:pt idx="0">
+                  <c:v>1568.3956187495346</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1522.5370809527169</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1514.6242539025059</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1448.3063104970304</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1416.5366742321485</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1382.5913567979078</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1352.1281761548335</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1316.1424428014113</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1292.227285364251</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1256.5927696390497</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1229.4369333409034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1216.4864065569802</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1177.9033231647918</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1160.0582035807654</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1133.0499991071747</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1126.0222379861807</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1106.6729262437348</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1086.0862804408871</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1064.1044902928011</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1047.7439145531227</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1026.778442658594</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1014.7575412000506</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>997.11005813176394</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>986.22185054767601</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>967.27810396229347</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>951.76583136790714</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>935.85143124581282</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>921.30762088650704</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>913.35673062950491</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>902.32259118873526</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>887.86164853068794</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>881.38319878055563</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>867.38188114877971</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>856.31606834535955</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>835.91280800603022</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>817.41771703364043</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>799.38993948084385</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>783.90908707552876</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>767.38704148583633</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>754.43717152141676</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>729.87584121464397</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>725.36750970623939</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>717.87462501523669</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>706.45534290239664</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>698.43410346668998</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>697.43410346668998</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>688.94979793160257</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>684.47166206396048</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>680.95909006382692</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>673.46326825153972</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>668.46311824386737</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>665.45383522701468</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>656.48955641615851</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>653.96694158426715</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>647.98130822981193</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>644.98126932838807</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>634.9664212342426</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>626.47768066658602</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>614.96584783011167</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>595.97345573965447</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>578.48887966849986</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>549</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>529</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>523</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>512</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>499</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>489</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>479</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>468</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>458</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>451</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>436</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>428</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>413</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>404</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>397</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>374</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>353</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>338</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>343</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>338</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>333</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>328</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>323</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>313</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>308</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>303</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>292</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>283</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>225</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-62F9-42E1-B5D8-74B8A0336C5B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2060104288"/>
+        <c:axId val="2060102368"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2060104288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2060102368"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2060102368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2486,7 +3833,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="928514991"/>
+        <c:crossAx val="2060104288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2623,6 +3970,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4210,6 +5597,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4291,16 +6194,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>315870</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>34024</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>8139</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>121946</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>325581</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>17851</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>157195</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4320,6 +6223,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>479118</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>12539</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>316926</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>175846</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45B9704F-F8FD-4EC3-1599-453DF2735FF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8879,7 +10818,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.44140625" style="8" customWidth="1"/>
@@ -8890,7 +10829,7 @@
     <col min="8" max="10" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
@@ -8918,8 +10857,14 @@
       <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>251</v>
       </c>
@@ -8947,9 +10892,14 @@
       <c r="I2" s="1">
         <v>11.258330249197703</v>
       </c>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="1">
+        <v>232.5</v>
+      </c>
+      <c r="K2" s="8">
+        <v>1568.3956187495346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>252</v>
       </c>
@@ -8977,9 +10927,14 @@
       <c r="I3" s="1">
         <v>33.774990747593108</v>
       </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="1">
+        <v>233.5</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1522.5370809527169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>253</v>
       </c>
@@ -9007,9 +10962,14 @@
       <c r="I4" s="1">
         <v>47.0540469389545</v>
       </c>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="1">
+        <v>234.5</v>
+      </c>
+      <c r="K4" s="8">
+        <v>1514.6242539025059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>254</v>
       </c>
@@ -9037,9 +10997,14 @@
       <c r="I5" s="1">
         <v>43.878620458411561</v>
       </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="1">
+        <v>235.5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1448.3063104970304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>255</v>
       </c>
@@ -9067,9 +11032,14 @@
       <c r="I6" s="1">
         <v>40.414518843273804</v>
       </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="1">
+        <v>236.5</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1416.5366742321485</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>256</v>
       </c>
@@ -9097,9 +11067,14 @@
       <c r="I7" s="1">
         <v>39.259818304894551</v>
       </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="1">
+        <v>237.5</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1382.5913567979078</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>257</v>
       </c>
@@ -9127,9 +11102,14 @@
       <c r="I8" s="1">
         <v>38.393792901110118</v>
       </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="1">
+        <v>238.5</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1352.1281761548335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>258</v>
       </c>
@@ -9157,9 +11137,14 @@
       <c r="I9" s="1">
         <v>30.02221399786054</v>
       </c>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="1">
+        <v>239.5</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1316.1424428014113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>259</v>
       </c>
@@ -9187,9 +11172,14 @@
       <c r="I10" s="1">
         <v>28.290163190291665</v>
       </c>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="1">
+        <v>240.5</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1292.227285364251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>260</v>
       </c>
@@ -9217,9 +11207,14 @@
       <c r="I11" s="1">
         <v>30.310889132455355</v>
       </c>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="1">
+        <v>241.5</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1256.5927696390497</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>261</v>
       </c>
@@ -9247,9 +11242,14 @@
       <c r="I12" s="1">
         <v>23.671361036774659</v>
       </c>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="1">
+        <v>242.5</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1229.4369333409034</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>262</v>
       </c>
@@ -9277,9 +11277,14 @@
       <c r="I13" s="1">
         <v>22.516660498395407</v>
       </c>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="1">
+        <v>243.5</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1216.4864065569802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>263</v>
       </c>
@@ -9307,9 +11312,14 @@
       <c r="I14" s="1">
         <v>23.96003617136947</v>
       </c>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="1">
+        <v>244.5</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1177.9033231647918</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>264</v>
       </c>
@@ -9337,9 +11347,14 @@
       <c r="I15" s="1">
         <v>20.495934556231717</v>
       </c>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="1">
+        <v>245.5</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1160.0582035807654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>265</v>
       </c>
@@ -9367,9 +11382,14 @@
       <c r="I16" s="1">
         <v>20.495934556231717</v>
       </c>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="1">
+        <v>246.5</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1133.0499991071747</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>266</v>
       </c>
@@ -9397,9 +11417,14 @@
       <c r="I17" s="1">
         <v>21.073284825421343</v>
       </c>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="1">
+        <v>247.5</v>
+      </c>
+      <c r="K17" s="8">
+        <v>1126.0222379861807</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>267</v>
       </c>
@@ -9427,9 +11452,14 @@
       <c r="I18" s="1">
         <v>17.320508075688775</v>
       </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="1">
+        <v>248.5</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1106.6729262437348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>268</v>
       </c>
@@ -9457,9 +11487,14 @@
       <c r="I19" s="1">
         <v>19.341234017852464</v>
       </c>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="1">
+        <v>249.5</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1086.0862804408871</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>269</v>
       </c>
@@ -9487,9 +11522,14 @@
       <c r="I20" s="1">
         <v>18.763883748662838</v>
       </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J20" s="1">
+        <v>250.5</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1064.1044902928011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>270</v>
       </c>
@@ -9517,9 +11557,14 @@
       <c r="I21" s="1">
         <v>15.01110699893027</v>
       </c>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="1">
+        <v>251.5</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1047.7439145531227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>271</v>
       </c>
@@ -9547,9 +11592,14 @@
       <c r="I22" s="1">
         <v>13.856406460551019</v>
       </c>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="1">
+        <v>252.5</v>
+      </c>
+      <c r="K22" s="8">
+        <v>1026.778442658594</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>272</v>
       </c>
@@ -9577,9 +11627,14 @@
       <c r="I23" s="1">
         <v>14.433756729740645</v>
       </c>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="1">
+        <v>253.5</v>
+      </c>
+      <c r="K23" s="8">
+        <v>1014.7575412000506</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>273</v>
       </c>
@@ -9607,9 +11662,14 @@
       <c r="I24" s="1">
         <v>18.186533479473212</v>
       </c>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="1">
+        <v>254.5</v>
+      </c>
+      <c r="K24" s="8">
+        <v>997.11005813176394</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>274</v>
       </c>
@@ -9637,9 +11697,14 @@
       <c r="I25" s="1">
         <v>15.299782133525083</v>
       </c>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J25" s="1">
+        <v>255.5</v>
+      </c>
+      <c r="K25" s="8">
+        <v>986.22185054767601</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>275</v>
       </c>
@@ -9667,9 +11732,14 @@
       <c r="I26" s="1">
         <v>13.567731325956206</v>
       </c>
-      <c r="J26" s="8"/>
-    </row>
-    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J26" s="1">
+        <v>256.5</v>
+      </c>
+      <c r="K26" s="8">
+        <v>967.27810396229347</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>276</v>
       </c>
@@ -9697,9 +11767,14 @@
       <c r="I27" s="1">
         <v>13.856406460551019</v>
       </c>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J27" s="1">
+        <v>257.5</v>
+      </c>
+      <c r="K27" s="8">
+        <v>951.76583136790714</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>277</v>
       </c>
@@ -9727,9 +11802,14 @@
       <c r="I28" s="1">
         <v>10.96965511460289</v>
       </c>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="1">
+        <v>258.5</v>
+      </c>
+      <c r="K28" s="8">
+        <v>935.85143124581282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>278</v>
       </c>
@@ -9757,9 +11837,14 @@
       <c r="I29" s="1">
         <v>12.413030787576954</v>
       </c>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J29" s="1">
+        <v>259.5</v>
+      </c>
+      <c r="K29" s="8">
+        <v>921.30762088650704</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>279</v>
       </c>
@@ -9787,9 +11872,14 @@
       <c r="I30" s="1">
         <v>10.680979980008077</v>
       </c>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="1">
+        <v>260.5</v>
+      </c>
+      <c r="K30" s="8">
+        <v>913.35673062950491</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>280</v>
       </c>
@@ -9817,9 +11907,14 @@
       <c r="I31" s="1">
         <v>11.835680518387329</v>
       </c>
-      <c r="J31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="1">
+        <v>261.5</v>
+      </c>
+      <c r="K31" s="8">
+        <v>902.32259118873526</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>281</v>
       </c>
@@ -9847,9 +11942,14 @@
       <c r="I32" s="1">
         <v>10.392304845413264</v>
       </c>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J32" s="1">
+        <v>262.5</v>
+      </c>
+      <c r="K32" s="8">
+        <v>887.86164853068794</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>282</v>
       </c>
@@ -9877,9 +11977,14 @@
       <c r="I33" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J33" s="1">
+        <v>263.5</v>
+      </c>
+      <c r="K33" s="8">
+        <v>881.38319878055563</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>283</v>
       </c>
@@ -9907,9 +12012,14 @@
       <c r="I34" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J34" s="1">
+        <v>264.5</v>
+      </c>
+      <c r="K34" s="8">
+        <v>867.38188114877971</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>284</v>
       </c>
@@ -9937,9 +12047,14 @@
       <c r="I35" s="1">
         <v>11.835680518387329</v>
       </c>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="1">
+        <v>265.5</v>
+      </c>
+      <c r="K35" s="8">
+        <v>856.31606834535955</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>286</v>
       </c>
@@ -9967,9 +12082,14 @@
       <c r="I36" s="1">
         <v>8.0829037686547611</v>
       </c>
-      <c r="J36" s="8"/>
-    </row>
-    <row r="37" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="1">
+        <v>267.5</v>
+      </c>
+      <c r="K36" s="8">
+        <v>835.91280800603022</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>288</v>
       </c>
@@ -9997,9 +12117,14 @@
       <c r="I37" s="1">
         <v>7.794228634059948</v>
       </c>
-      <c r="J37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="1">
+        <v>269.5</v>
+      </c>
+      <c r="K37" s="8">
+        <v>817.41771703364043</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>290</v>
       </c>
@@ -10027,9 +12152,14 @@
       <c r="I38" s="1">
         <v>8.9489291724392004</v>
       </c>
-      <c r="J38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="1">
+        <v>271.5</v>
+      </c>
+      <c r="K38" s="8">
+        <v>799.38993948084385</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>292</v>
       </c>
@@ -10057,9 +12187,14 @@
       <c r="I39" s="1">
         <v>8.0829037686547611</v>
       </c>
-      <c r="J39" s="8"/>
-    </row>
-    <row r="40" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="1">
+        <v>273.5</v>
+      </c>
+      <c r="K39" s="8">
+        <v>783.90908707552876</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>294</v>
       </c>
@@ -10087,9 +12222,14 @@
       <c r="I40" s="1">
         <v>8.9489291724392004</v>
       </c>
-      <c r="J40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J40" s="1">
+        <v>275.5</v>
+      </c>
+      <c r="K40" s="8">
+        <v>767.38704148583633</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>296</v>
       </c>
@@ -10117,9 +12257,14 @@
       <c r="I41" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="1">
+        <v>277.5</v>
+      </c>
+      <c r="K41" s="8">
+        <v>754.43717152141676</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>299</v>
       </c>
@@ -10147,9 +12292,14 @@
       <c r="I42" s="1">
         <v>9.2376043070340135</v>
       </c>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J42" s="1">
+        <v>280.5</v>
+      </c>
+      <c r="K42" s="8">
+        <v>729.87584121464397</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>300</v>
       </c>
@@ -10177,9 +12327,14 @@
       <c r="I43" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J43" s="8"/>
-    </row>
-    <row r="44" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J43" s="1">
+        <v>281.5</v>
+      </c>
+      <c r="K43" s="8">
+        <v>725.36750970623939</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>301</v>
       </c>
@@ -10207,9 +12362,14 @@
       <c r="I44" s="1">
         <v>9.2376043070340135</v>
       </c>
-      <c r="J44" s="8"/>
-    </row>
-    <row r="45" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J44" s="1">
+        <v>282.5</v>
+      </c>
+      <c r="K44" s="8">
+        <v>717.87462501523669</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>302</v>
       </c>
@@ -10237,9 +12397,14 @@
       <c r="I45" s="1">
         <v>5.4848275573014451</v>
       </c>
-      <c r="J45" s="8"/>
-    </row>
-    <row r="46" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J45" s="1">
+        <v>283.5</v>
+      </c>
+      <c r="K45" s="8">
+        <v>706.45534290239664</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>303</v>
       </c>
@@ -10267,9 +12432,14 @@
       <c r="I46" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J46" s="1">
+        <v>284.5</v>
+      </c>
+      <c r="K46" s="8">
+        <v>698.43410346668998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>304</v>
       </c>
@@ -10297,9 +12467,14 @@
       <c r="I47" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J47" s="8"/>
-    </row>
-    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J47" s="1">
+        <v>285.5</v>
+      </c>
+      <c r="K47" s="8">
+        <v>697.43410346668998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>305</v>
       </c>
@@ -10327,9 +12502,14 @@
       <c r="I48" s="1">
         <v>5.7735026918962582</v>
       </c>
-      <c r="J48" s="8"/>
-    </row>
-    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="1">
+        <v>286.5</v>
+      </c>
+      <c r="K48" s="8">
+        <v>688.94979793160257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>306</v>
       </c>
@@ -10357,9 +12537,14 @@
       <c r="I49" s="1">
         <v>4.3301270189221936</v>
       </c>
-      <c r="J49" s="8"/>
-    </row>
-    <row r="50" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J49" s="1">
+        <v>287.5</v>
+      </c>
+      <c r="K49" s="8">
+        <v>684.47166206396048</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>307</v>
       </c>
@@ -10387,9 +12572,14 @@
       <c r="I50" s="1">
         <v>5.196152422706632</v>
       </c>
-      <c r="J50" s="8"/>
-    </row>
-    <row r="51" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J50" s="1">
+        <v>288.5</v>
+      </c>
+      <c r="K50" s="8">
+        <v>680.95909006382692</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>308</v>
       </c>
@@ -10417,9 +12607,14 @@
       <c r="I51" s="1">
         <v>4.9074772881118189</v>
       </c>
-      <c r="J51" s="8"/>
-    </row>
-    <row r="52" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J51" s="1">
+        <v>289.5</v>
+      </c>
+      <c r="K51" s="8">
+        <v>673.46326825153972</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>309</v>
       </c>
@@ -10447,9 +12642,14 @@
       <c r="I52" s="1">
         <v>4.9074772881118189</v>
       </c>
-      <c r="J52" s="8"/>
-    </row>
-    <row r="53" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J52" s="1">
+        <v>290.5</v>
+      </c>
+      <c r="K52" s="8">
+        <v>668.46311824386737</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>310</v>
       </c>
@@ -10477,9 +12677,14 @@
       <c r="I53" s="1">
         <v>5.4848275573014451</v>
       </c>
-      <c r="J53" s="8"/>
-    </row>
-    <row r="54" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J53" s="1">
+        <v>291.5</v>
+      </c>
+      <c r="K53" s="8">
+        <v>665.45383522701468</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>311</v>
       </c>
@@ -10507,9 +12712,14 @@
       <c r="I54" s="1">
         <v>2.598076211353316</v>
       </c>
-      <c r="J54" s="8"/>
-    </row>
-    <row r="55" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J54" s="1">
+        <v>292.5</v>
+      </c>
+      <c r="K54" s="8">
+        <v>656.48955641615851</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>312</v>
       </c>
@@ -10537,9 +12747,14 @@
       <c r="I55" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J55" s="8"/>
-    </row>
-    <row r="56" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J55" s="1">
+        <v>293.5</v>
+      </c>
+      <c r="K55" s="8">
+        <v>653.96694158426715</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>313</v>
       </c>
@@ -10567,9 +12782,14 @@
       <c r="I56" s="1">
         <v>3.4641016151377548</v>
       </c>
-      <c r="J56" s="8"/>
-    </row>
-    <row r="57" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J56" s="1">
+        <v>294.5</v>
+      </c>
+      <c r="K56" s="8">
+        <v>647.98130822981193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>314</v>
       </c>
@@ -10597,9 +12817,14 @@
       <c r="I57" s="1">
         <v>3.4641016151377548</v>
       </c>
-      <c r="J57" s="8"/>
-    </row>
-    <row r="58" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J57" s="1">
+        <v>295.5</v>
+      </c>
+      <c r="K57" s="8">
+        <v>644.98126932838807</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>316</v>
       </c>
@@ -10627,9 +12852,14 @@
       <c r="I58" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J58" s="8"/>
-    </row>
-    <row r="59" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J58" s="1">
+        <v>297.5</v>
+      </c>
+      <c r="K58" s="8">
+        <v>634.9664212342426</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>318</v>
       </c>
@@ -10657,9 +12887,14 @@
       <c r="I59" s="1">
         <v>3.7527767497325675</v>
       </c>
-      <c r="J59" s="8"/>
-    </row>
-    <row r="60" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J59" s="1">
+        <v>299.5</v>
+      </c>
+      <c r="K59" s="8">
+        <v>626.47768066658602</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>320</v>
       </c>
@@ -10687,9 +12922,14 @@
       <c r="I60" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J60" s="8"/>
-    </row>
-    <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J60" s="1">
+        <v>301.5</v>
+      </c>
+      <c r="K60" s="8">
+        <v>614.96584783011167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>325</v>
       </c>
@@ -10717,9 +12957,14 @@
       <c r="I61" s="1">
         <v>4.0414518843273806</v>
       </c>
-      <c r="J61" s="8"/>
-    </row>
-    <row r="62" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J61" s="1">
+        <v>306.5</v>
+      </c>
+      <c r="K61" s="8">
+        <v>595.97345573965447</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>330</v>
       </c>
@@ -10747,9 +12992,14 @@
       <c r="I62" s="1">
         <v>2.598076211353316</v>
       </c>
-      <c r="J62" s="8"/>
-    </row>
-    <row r="63" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J62" s="1">
+        <v>311.5</v>
+      </c>
+      <c r="K62" s="8">
+        <v>578.48887966849986</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>335</v>
       </c>
@@ -10774,9 +13024,14 @@
       <c r="I63" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J63" s="8"/>
-    </row>
-    <row r="64" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J63" s="1">
+        <v>316.5</v>
+      </c>
+      <c r="K63" s="8">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>340</v>
       </c>
@@ -10801,9 +13056,14 @@
       <c r="I64" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J64" s="8"/>
-    </row>
-    <row r="65" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J64" s="1">
+        <v>321.5</v>
+      </c>
+      <c r="K64" s="8">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>345</v>
       </c>
@@ -10828,9 +13088,14 @@
       <c r="I65" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J65" s="8"/>
-    </row>
-    <row r="66" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J65" s="1">
+        <v>326.5</v>
+      </c>
+      <c r="K65" s="8">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>350</v>
       </c>
@@ -10855,9 +13120,14 @@
       <c r="I66" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J66" s="8"/>
-    </row>
-    <row r="67" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J66" s="1">
+        <v>331.5</v>
+      </c>
+      <c r="K66" s="8">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>355</v>
       </c>
@@ -10882,9 +13152,14 @@
       <c r="I67" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J67" s="8"/>
-    </row>
-    <row r="68" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J67" s="1">
+        <v>336.5</v>
+      </c>
+      <c r="K67" s="8">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>360</v>
       </c>
@@ -10909,9 +13184,14 @@
       <c r="I68" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J68" s="8"/>
-    </row>
-    <row r="69" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J68" s="1">
+        <v>341.5</v>
+      </c>
+      <c r="K68" s="8">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>365</v>
       </c>
@@ -10936,9 +13216,14 @@
       <c r="I69" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J69" s="8"/>
-    </row>
-    <row r="70" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J69" s="1">
+        <v>346.5</v>
+      </c>
+      <c r="K69" s="8">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>370</v>
       </c>
@@ -10963,9 +13248,14 @@
       <c r="I70" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J70" s="8"/>
-    </row>
-    <row r="71" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J70" s="1">
+        <v>351.5</v>
+      </c>
+      <c r="K70" s="8">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>375</v>
       </c>
@@ -10990,9 +13280,14 @@
       <c r="I71" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J71" s="8"/>
-    </row>
-    <row r="72" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J71" s="1">
+        <v>356.5</v>
+      </c>
+      <c r="K71" s="8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>380</v>
       </c>
@@ -11017,9 +13312,14 @@
       <c r="I72" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J72" s="8"/>
-    </row>
-    <row r="73" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J72" s="1">
+        <v>361.5</v>
+      </c>
+      <c r="K72" s="8">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>385</v>
       </c>
@@ -11044,9 +13344,14 @@
       <c r="I73" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J73" s="8"/>
-    </row>
-    <row r="74" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J73" s="1">
+        <v>366.5</v>
+      </c>
+      <c r="K73" s="8">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>390</v>
       </c>
@@ -11071,9 +13376,14 @@
       <c r="I74" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J74" s="8"/>
-    </row>
-    <row r="75" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J74" s="1">
+        <v>371.5</v>
+      </c>
+      <c r="K74" s="8">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>395</v>
       </c>
@@ -11098,9 +13408,14 @@
       <c r="I75" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J75" s="8"/>
-    </row>
-    <row r="76" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J75" s="1">
+        <v>376.5</v>
+      </c>
+      <c r="K75" s="8">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>400</v>
       </c>
@@ -11125,9 +13440,14 @@
       <c r="I76" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J76" s="8"/>
-    </row>
-    <row r="77" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J76" s="1">
+        <v>381.5</v>
+      </c>
+      <c r="K76" s="8">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>405</v>
       </c>
@@ -11152,9 +13472,14 @@
       <c r="I77" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J77" s="8"/>
-    </row>
-    <row r="78" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J77" s="1">
+        <v>386.5</v>
+      </c>
+      <c r="K77" s="8">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>410</v>
       </c>
@@ -11179,9 +13504,14 @@
       <c r="I78" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J78" s="8"/>
-    </row>
-    <row r="79" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J78" s="1">
+        <v>391.5</v>
+      </c>
+      <c r="K78" s="8">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>415</v>
       </c>
@@ -11206,8 +13536,14 @@
       <c r="I79" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J79" s="1">
+        <v>396.5</v>
+      </c>
+      <c r="K79" s="8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>420</v>
       </c>
@@ -11232,8 +13568,14 @@
       <c r="I80" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J80" s="1">
+        <v>401.5</v>
+      </c>
+      <c r="K80" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>425</v>
       </c>
@@ -11258,8 +13600,16 @@
       <c r="I81" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J81" s="1">
+        <f>F81-5</f>
+        <v>401.5</v>
+      </c>
+      <c r="K81" s="6">
+        <f>G81-5</f>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>430</v>
       </c>
@@ -11284,8 +13634,16 @@
       <c r="I82" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J82" s="1">
+        <f t="shared" ref="J82:J117" si="0">F82-5</f>
+        <v>406.5</v>
+      </c>
+      <c r="K82" s="6">
+        <f t="shared" ref="K82:K117" si="1">G82-5</f>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>435</v>
       </c>
@@ -11310,8 +13668,16 @@
       <c r="I83" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J83" s="1">
+        <f t="shared" si="0"/>
+        <v>411.5</v>
+      </c>
+      <c r="K83" s="6">
+        <f t="shared" si="1"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>440</v>
       </c>
@@ -11336,8 +13702,16 @@
       <c r="I84" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J84" s="1">
+        <f t="shared" si="0"/>
+        <v>416.5</v>
+      </c>
+      <c r="K84" s="6">
+        <f t="shared" si="1"/>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>445</v>
       </c>
@@ -11362,8 +13736,16 @@
       <c r="I85" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J85" s="1">
+        <f t="shared" si="0"/>
+        <v>421.5</v>
+      </c>
+      <c r="K85" s="6">
+        <f t="shared" si="1"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>450</v>
       </c>
@@ -11388,8 +13770,16 @@
       <c r="I86" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J86" s="1">
+        <f t="shared" si="0"/>
+        <v>426.5</v>
+      </c>
+      <c r="K86" s="6">
+        <f t="shared" si="1"/>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>460</v>
       </c>
@@ -11414,8 +13804,16 @@
       <c r="I87" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J87" s="1">
+        <f t="shared" si="0"/>
+        <v>436.5</v>
+      </c>
+      <c r="K87" s="6">
+        <f t="shared" si="1"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>470</v>
       </c>
@@ -11440,8 +13838,16 @@
       <c r="I88" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J88" s="1">
+        <f t="shared" si="0"/>
+        <v>446.5</v>
+      </c>
+      <c r="K88" s="6">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>480</v>
       </c>
@@ -11466,8 +13872,16 @@
       <c r="I89" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J89" s="1">
+        <f t="shared" si="0"/>
+        <v>456.5</v>
+      </c>
+      <c r="K89" s="6">
+        <f t="shared" si="1"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>490</v>
       </c>
@@ -11492,8 +13906,16 @@
       <c r="I90" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J90" s="1">
+        <f t="shared" si="0"/>
+        <v>466.5</v>
+      </c>
+      <c r="K90" s="6">
+        <f t="shared" si="1"/>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>500</v>
       </c>
@@ -11518,8 +13940,16 @@
       <c r="I91" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J91" s="1">
+        <f t="shared" si="0"/>
+        <v>476.5</v>
+      </c>
+      <c r="K91" s="6">
+        <f t="shared" si="1"/>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>510</v>
       </c>
@@ -11544,8 +13974,16 @@
       <c r="I92" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J92" s="1">
+        <f t="shared" si="0"/>
+        <v>486.5</v>
+      </c>
+      <c r="K92" s="6">
+        <f t="shared" si="1"/>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>520</v>
       </c>
@@ -11570,8 +14008,16 @@
       <c r="I93" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J93" s="1">
+        <f t="shared" si="0"/>
+        <v>496.5</v>
+      </c>
+      <c r="K93" s="6">
+        <f t="shared" si="1"/>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>530</v>
       </c>
@@ -11596,8 +14042,16 @@
       <c r="I94" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J94" s="1">
+        <f t="shared" si="0"/>
+        <v>506.5</v>
+      </c>
+      <c r="K94" s="6">
+        <f t="shared" si="1"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>540</v>
       </c>
@@ -11622,8 +14076,16 @@
       <c r="I95" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J95" s="1">
+        <f t="shared" si="0"/>
+        <v>516.5</v>
+      </c>
+      <c r="K95" s="6">
+        <f t="shared" si="1"/>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>550</v>
       </c>
@@ -11648,8 +14110,16 @@
       <c r="I96" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J96" s="1">
+        <f t="shared" si="0"/>
+        <v>526.5</v>
+      </c>
+      <c r="K96" s="6">
+        <f t="shared" si="1"/>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>560</v>
       </c>
@@ -11674,8 +14144,16 @@
       <c r="I97" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J97" s="1">
+        <f t="shared" si="0"/>
+        <v>536.5</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="1"/>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>570</v>
       </c>
@@ -11700,8 +14178,16 @@
       <c r="I98" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J98" s="1">
+        <f t="shared" si="0"/>
+        <v>546.5</v>
+      </c>
+      <c r="K98" s="6">
+        <f t="shared" si="1"/>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>580</v>
       </c>
@@ -11726,8 +14212,16 @@
       <c r="I99" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J99" s="1">
+        <f t="shared" si="0"/>
+        <v>556.5</v>
+      </c>
+      <c r="K99" s="6">
+        <f t="shared" si="1"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>590</v>
       </c>
@@ -11752,8 +14246,16 @@
       <c r="I100" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J100" s="1">
+        <f t="shared" si="0"/>
+        <v>566.5</v>
+      </c>
+      <c r="K100" s="6">
+        <f t="shared" si="1"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>600</v>
       </c>
@@ -11778,8 +14280,16 @@
       <c r="I101" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J101" s="1">
+        <f t="shared" si="0"/>
+        <v>576.5</v>
+      </c>
+      <c r="K101" s="6">
+        <f t="shared" si="1"/>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>620</v>
       </c>
@@ -11804,8 +14314,16 @@
       <c r="I102" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J102" s="1">
+        <f t="shared" si="0"/>
+        <v>596.5</v>
+      </c>
+      <c r="K102" s="6">
+        <f t="shared" si="1"/>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>640</v>
       </c>
@@ -11830,8 +14348,16 @@
       <c r="I103" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J103" s="1">
+        <f t="shared" si="0"/>
+        <v>616.5</v>
+      </c>
+      <c r="K103" s="6">
+        <f t="shared" si="1"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>660</v>
       </c>
@@ -11856,8 +14382,16 @@
       <c r="I104" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J104" s="1">
+        <f t="shared" si="0"/>
+        <v>636.5</v>
+      </c>
+      <c r="K104" s="6">
+        <f t="shared" si="1"/>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>680</v>
       </c>
@@ -11882,8 +14416,16 @@
       <c r="I105" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J105" s="1">
+        <f t="shared" si="0"/>
+        <v>656.5</v>
+      </c>
+      <c r="K105" s="6">
+        <f t="shared" si="1"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>700</v>
       </c>
@@ -11908,8 +14450,16 @@
       <c r="I106" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J106" s="1">
+        <f t="shared" si="0"/>
+        <v>676.5</v>
+      </c>
+      <c r="K106" s="6">
+        <f t="shared" si="1"/>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>750</v>
       </c>
@@ -11934,8 +14484,16 @@
       <c r="I107" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J107" s="1">
+        <f t="shared" si="0"/>
+        <v>726.5</v>
+      </c>
+      <c r="K107" s="6">
+        <f t="shared" si="1"/>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>800</v>
       </c>
@@ -11960,8 +14518,16 @@
       <c r="I108" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J108" s="1">
+        <f t="shared" si="0"/>
+        <v>776.5</v>
+      </c>
+      <c r="K108" s="6">
+        <f t="shared" si="1"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>850</v>
       </c>
@@ -11986,8 +14552,16 @@
       <c r="I109" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J109" s="1">
+        <f t="shared" si="0"/>
+        <v>826.5</v>
+      </c>
+      <c r="K109" s="6">
+        <f t="shared" si="1"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>900</v>
       </c>
@@ -12012,8 +14586,16 @@
       <c r="I110" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J110" s="1">
+        <f t="shared" si="0"/>
+        <v>876.5</v>
+      </c>
+      <c r="K110" s="6">
+        <f t="shared" si="1"/>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>1000</v>
       </c>
@@ -12038,8 +14620,16 @@
       <c r="I111" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J111" s="1">
+        <f t="shared" si="0"/>
+        <v>976.5</v>
+      </c>
+      <c r="K111" s="6">
+        <f t="shared" si="1"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>1100</v>
       </c>
@@ -12064,8 +14654,16 @@
       <c r="I112" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J112" s="1">
+        <f t="shared" si="0"/>
+        <v>1076.5</v>
+      </c>
+      <c r="K112" s="6">
+        <f t="shared" si="1"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>1200</v>
       </c>
@@ -12090,8 +14688,16 @@
       <c r="I113" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J113" s="1">
+        <f t="shared" si="0"/>
+        <v>1176.5</v>
+      </c>
+      <c r="K113" s="6">
+        <f t="shared" si="1"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>1300</v>
       </c>
@@ -12116,8 +14722,16 @@
       <c r="I114" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J114" s="1">
+        <f t="shared" si="0"/>
+        <v>1276.5</v>
+      </c>
+      <c r="K114" s="6">
+        <f t="shared" si="1"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>1400</v>
       </c>
@@ -12142,8 +14756,16 @@
       <c r="I115" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J115" s="1">
+        <f t="shared" si="0"/>
+        <v>1376.5</v>
+      </c>
+      <c r="K115" s="6">
+        <f t="shared" si="1"/>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>1500</v>
       </c>
@@ -12168,8 +14790,16 @@
       <c r="I116" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J116" s="1">
+        <f t="shared" si="0"/>
+        <v>1476.5</v>
+      </c>
+      <c r="K116" s="6">
+        <f t="shared" si="1"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>1650</v>
       </c>
@@ -12194,34 +14824,42 @@
       <c r="I117" s="9">
         <v>0.11547005383792516</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J117" s="1">
+        <f t="shared" si="0"/>
+        <v>1626.5</v>
+      </c>
+      <c r="K117" s="6">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7"/>
     </row>
-    <row r="119" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7"/>
     </row>
-    <row r="120" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7"/>
     </row>
-    <row r="121" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7"/>
     </row>
-    <row r="122" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7"/>
     </row>
-    <row r="123" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7"/>
     </row>
-    <row r="124" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7"/>
     </row>
-    <row r="125" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7"/>
     </row>
-    <row r="126" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="129" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="130" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -12239,7 +14877,9 @@
     <col min="1" max="2" width="12.44140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="5" width="12.44140625" style="8" customWidth="1"/>
-    <col min="6" max="11" width="12.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625"/>
+    <col min="8" max="11" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -12261,7 +14901,7 @@
       <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -14549,8 +17189,8 @@
       <c r="F79" s="1">
         <v>396.5</v>
       </c>
-      <c r="G79" s="1">
-        <v>396</v>
+      <c r="G79" s="8">
+        <v>397</v>
       </c>
       <c r="H79" s="9">
         <v>0.11547005383792516</v>
@@ -14575,8 +17215,8 @@
       <c r="F80" s="1">
         <v>401.5</v>
       </c>
-      <c r="G80" s="1">
-        <v>393</v>
+      <c r="G80" s="8">
+        <v>400</v>
       </c>
       <c r="H80" s="9">
         <v>0.11547005383792516</v>
@@ -14599,10 +17239,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F81" s="1">
-        <v>406.5</v>
-      </c>
-      <c r="G81" s="1">
-        <v>391</v>
+        <v>401.5</v>
+      </c>
+      <c r="G81" s="6">
+        <v>393</v>
       </c>
       <c r="H81" s="9">
         <v>0.11547005383792516</v>
@@ -14625,10 +17265,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F82" s="1">
-        <v>411.5</v>
-      </c>
-      <c r="G82" s="1">
-        <v>388</v>
+        <v>406.5</v>
+      </c>
+      <c r="G82" s="6">
+        <v>390</v>
       </c>
       <c r="H82" s="9">
         <v>0.11547005383792516</v>
@@ -14651,10 +17291,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F83" s="1">
-        <v>416.5</v>
-      </c>
-      <c r="G83" s="1">
-        <v>383</v>
+        <v>411.5</v>
+      </c>
+      <c r="G83" s="6">
+        <v>385</v>
       </c>
       <c r="H83" s="9">
         <v>0.11547005383792516</v>
@@ -14677,10 +17317,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F84" s="1">
-        <v>421.5</v>
-      </c>
-      <c r="G84" s="1">
-        <v>380</v>
+        <v>416.5</v>
+      </c>
+      <c r="G84" s="6">
+        <v>382</v>
       </c>
       <c r="H84" s="9">
         <v>0.11547005383792516</v>
@@ -14703,10 +17343,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F85" s="1">
-        <v>426.5</v>
-      </c>
-      <c r="G85" s="1">
-        <v>376</v>
+        <v>421.5</v>
+      </c>
+      <c r="G85" s="6">
+        <v>378</v>
       </c>
       <c r="H85" s="9">
         <v>0.11547005383792516</v>
@@ -14729,10 +17369,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F86" s="1">
-        <v>431.5</v>
-      </c>
-      <c r="G86" s="1">
-        <v>372</v>
+        <v>426.5</v>
+      </c>
+      <c r="G86" s="6">
+        <v>374</v>
       </c>
       <c r="H86" s="9">
         <v>0.11547005383792516</v>
@@ -14755,10 +17395,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F87" s="1">
-        <v>441.5</v>
-      </c>
-      <c r="G87" s="1">
-        <v>363</v>
+        <v>436.5</v>
+      </c>
+      <c r="G87" s="6">
+        <v>365</v>
       </c>
       <c r="H87" s="9">
         <v>0.11547005383792516</v>
@@ -14781,10 +17421,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F88" s="1">
-        <v>451.5</v>
-      </c>
-      <c r="G88" s="1">
-        <v>358</v>
+        <v>446.5</v>
+      </c>
+      <c r="G88" s="6">
+        <v>360</v>
       </c>
       <c r="H88" s="9">
         <v>0.11547005383792516</v>
@@ -14807,10 +17447,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F89" s="1">
-        <v>461.5</v>
-      </c>
-      <c r="G89" s="1">
-        <v>351</v>
+        <v>456.5</v>
+      </c>
+      <c r="G89" s="6">
+        <v>353</v>
       </c>
       <c r="H89" s="9">
         <v>0.11547005383792516</v>
@@ -14833,10 +17473,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F90" s="1">
-        <v>471.5</v>
-      </c>
-      <c r="G90" s="1">
-        <v>336</v>
+        <v>466.5</v>
+      </c>
+      <c r="G90" s="6">
+        <v>338</v>
       </c>
       <c r="H90" s="9">
         <v>0.11547005383792516</v>
@@ -14859,10 +17499,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F91" s="1">
-        <v>481.5</v>
-      </c>
-      <c r="G91" s="1">
-        <v>341</v>
+        <v>476.5</v>
+      </c>
+      <c r="G91" s="6">
+        <v>343</v>
       </c>
       <c r="H91" s="9">
         <v>0.11547005383792516</v>
@@ -14885,10 +17525,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F92" s="1">
-        <v>491.5</v>
-      </c>
-      <c r="G92" s="1">
-        <v>336</v>
+        <v>486.5</v>
+      </c>
+      <c r="G92" s="6">
+        <v>338</v>
       </c>
       <c r="H92" s="9">
         <v>0.11547005383792516</v>
@@ -14911,10 +17551,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F93" s="1">
-        <v>501.5</v>
-      </c>
-      <c r="G93" s="1">
-        <v>331</v>
+        <v>496.5</v>
+      </c>
+      <c r="G93" s="6">
+        <v>333</v>
       </c>
       <c r="H93" s="9">
         <v>0.11547005383792516</v>
@@ -14937,10 +17577,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F94" s="1">
-        <v>511.5</v>
-      </c>
-      <c r="G94" s="1">
-        <v>326</v>
+        <v>506.5</v>
+      </c>
+      <c r="G94" s="6">
+        <v>328</v>
       </c>
       <c r="H94" s="9">
         <v>0.11547005383792516</v>
@@ -14963,10 +17603,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F95" s="1">
-        <v>521.5</v>
-      </c>
-      <c r="G95" s="1">
-        <v>321</v>
+        <v>516.5</v>
+      </c>
+      <c r="G95" s="6">
+        <v>323</v>
       </c>
       <c r="H95" s="9">
         <v>0.11547005383792516</v>
@@ -14989,10 +17629,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F96" s="1">
-        <v>531.5</v>
-      </c>
-      <c r="G96" s="1">
-        <v>316</v>
+        <v>526.5</v>
+      </c>
+      <c r="G96" s="6">
+        <v>318</v>
       </c>
       <c r="H96" s="9">
         <v>0.11547005383792516</v>
@@ -15015,10 +17655,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F97" s="1">
-        <v>541.5</v>
-      </c>
-      <c r="G97" s="1">
-        <v>316</v>
+        <v>536.5</v>
+      </c>
+      <c r="G97" s="6">
+        <v>318</v>
       </c>
       <c r="H97" s="9">
         <v>0.11547005383792516</v>
@@ -15041,10 +17681,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F98" s="1">
-        <v>551.5</v>
-      </c>
-      <c r="G98" s="1">
-        <v>311</v>
+        <v>546.5</v>
+      </c>
+      <c r="G98" s="6">
+        <v>313</v>
       </c>
       <c r="H98" s="9">
         <v>0.11547005383792516</v>
@@ -15067,10 +17707,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F99" s="1">
-        <v>561.5</v>
-      </c>
-      <c r="G99" s="1">
-        <v>308</v>
+        <v>556.5</v>
+      </c>
+      <c r="G99" s="6">
+        <v>310</v>
       </c>
       <c r="H99" s="9">
         <v>0.11547005383792516</v>
@@ -15093,10 +17733,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F100" s="1">
-        <v>571.5</v>
-      </c>
-      <c r="G100" s="1">
-        <v>306</v>
+        <v>566.5</v>
+      </c>
+      <c r="G100" s="6">
+        <v>308</v>
       </c>
       <c r="H100" s="9">
         <v>0.11547005383792516</v>
@@ -15119,10 +17759,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F101" s="1">
-        <v>581.5</v>
-      </c>
-      <c r="G101" s="1">
-        <v>301</v>
+        <v>576.5</v>
+      </c>
+      <c r="G101" s="6">
+        <v>303</v>
       </c>
       <c r="H101" s="9">
         <v>0.11547005383792516</v>
@@ -15145,10 +17785,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F102" s="1">
-        <v>601.5</v>
-      </c>
-      <c r="G102" s="1">
-        <v>296</v>
+        <v>596.5</v>
+      </c>
+      <c r="G102" s="6">
+        <v>298</v>
       </c>
       <c r="H102" s="9">
         <v>0.11547005383792516</v>
@@ -15171,10 +17811,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F103" s="1">
-        <v>621.5</v>
-      </c>
-      <c r="G103" s="1">
-        <v>290</v>
+        <v>616.5</v>
+      </c>
+      <c r="G103" s="6">
+        <v>292</v>
       </c>
       <c r="H103" s="9">
         <v>0.11547005383792516</v>
@@ -15197,10 +17837,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F104" s="1">
-        <v>641.5</v>
-      </c>
-      <c r="G104" s="1">
-        <v>289</v>
+        <v>636.5</v>
+      </c>
+      <c r="G104" s="6">
+        <v>291</v>
       </c>
       <c r="H104" s="9">
         <v>0.11547005383792516</v>
@@ -15223,10 +17863,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F105" s="1">
-        <v>661.5</v>
-      </c>
-      <c r="G105" s="1">
-        <v>283</v>
+        <v>656.5</v>
+      </c>
+      <c r="G105" s="6">
+        <v>285</v>
       </c>
       <c r="H105" s="9">
         <v>0.11547005383792516</v>
@@ -15249,10 +17889,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F106" s="1">
-        <v>681.5</v>
-      </c>
-      <c r="G106" s="1">
-        <v>281</v>
+        <v>676.5</v>
+      </c>
+      <c r="G106" s="6">
+        <v>283</v>
       </c>
       <c r="H106" s="9">
         <v>0.11547005383792516</v>
@@ -15275,10 +17915,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F107" s="1">
-        <v>731.5</v>
-      </c>
-      <c r="G107" s="1">
-        <v>271</v>
+        <v>726.5</v>
+      </c>
+      <c r="G107" s="6">
+        <v>273</v>
       </c>
       <c r="H107" s="9">
         <v>0.11547005383792516</v>
@@ -15301,10 +17941,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F108" s="1">
-        <v>781.5</v>
-      </c>
-      <c r="G108" s="1">
-        <v>264</v>
+        <v>776.5</v>
+      </c>
+      <c r="G108" s="6">
+        <v>266</v>
       </c>
       <c r="H108" s="9">
         <v>0.11547005383792516</v>
@@ -15327,10 +17967,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F109" s="1">
-        <v>831.5</v>
-      </c>
-      <c r="G109" s="1">
-        <v>259</v>
+        <v>826.5</v>
+      </c>
+      <c r="G109" s="6">
+        <v>261</v>
       </c>
       <c r="H109" s="9">
         <v>0.11547005383792516</v>
@@ -15353,10 +17993,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F110" s="1">
-        <v>881.5</v>
-      </c>
-      <c r="G110" s="1">
-        <v>255</v>
+        <v>876.5</v>
+      </c>
+      <c r="G110" s="6">
+        <v>257</v>
       </c>
       <c r="H110" s="9">
         <v>0.11547005383792516</v>
@@ -15379,10 +18019,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F111" s="1">
-        <v>981.5</v>
-      </c>
-      <c r="G111" s="1">
-        <v>246</v>
+        <v>976.5</v>
+      </c>
+      <c r="G111" s="6">
+        <v>248</v>
       </c>
       <c r="H111" s="9">
         <v>0.11547005383792516</v>
@@ -15405,10 +18045,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F112" s="1">
-        <v>1081.5</v>
-      </c>
-      <c r="G112" s="1">
-        <v>240</v>
+        <v>1076.5</v>
+      </c>
+      <c r="G112" s="6">
+        <v>242</v>
       </c>
       <c r="H112" s="9">
         <v>0.11547005383792516</v>
@@ -15431,10 +18071,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F113" s="1">
-        <v>1181.5</v>
-      </c>
-      <c r="G113" s="1">
-        <v>236</v>
+        <v>1176.5</v>
+      </c>
+      <c r="G113" s="6">
+        <v>238</v>
       </c>
       <c r="H113" s="9">
         <v>0.11547005383792516</v>
@@ -15457,10 +18097,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F114" s="1">
-        <v>1281.5</v>
-      </c>
-      <c r="G114" s="1">
-        <v>233</v>
+        <v>1276.5</v>
+      </c>
+      <c r="G114" s="6">
+        <v>235</v>
       </c>
       <c r="H114" s="9">
         <v>0.11547005383792516</v>
@@ -15483,10 +18123,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F115" s="1">
-        <v>1381.5</v>
-      </c>
-      <c r="G115" s="1">
-        <v>229</v>
+        <v>1376.5</v>
+      </c>
+      <c r="G115" s="6">
+        <v>231</v>
       </c>
       <c r="H115" s="9">
         <v>0.11547005383792516</v>
@@ -15509,10 +18149,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F116" s="1">
-        <v>1481.5</v>
-      </c>
-      <c r="G116" s="1">
-        <v>227</v>
+        <v>1476.5</v>
+      </c>
+      <c r="G116" s="6">
+        <v>229</v>
       </c>
       <c r="H116" s="9">
         <v>0.11547005383792516</v>
@@ -15535,10 +18175,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F117" s="1">
-        <v>1631.5</v>
-      </c>
-      <c r="G117" s="1">
-        <v>223</v>
+        <v>1626.5</v>
+      </c>
+      <c r="G117" s="6">
+        <v>225</v>
       </c>
       <c r="H117" s="9">
         <v>0.11547005383792516</v>

--- a/Laboratorio/esperienza2/prove/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/prove/esperienza2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\Documents\UNIVERSITA'\III ANNO\Laboratorio-di-Ottica\Laboratorio\esperienza2\prove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD6459E-ED43-4A27-A1BA-86982DD69547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B24BBBB-AC86-4385-A63B-D45DF0BFB61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t xml:space="preserve"> L</t>
   </si>
@@ -2307,9 +2307,6 @@
               <c:f>Dati!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>p</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2346,355 +2343,118 @@
             <c:numRef>
               <c:f>Dati!$J$2:$J$130</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="129"/>
-                <c:pt idx="0">
-                  <c:v>232.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>233.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>234.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>235.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>236.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>237.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>238.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>239.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>240.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>241.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>242.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>243.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>244.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>245.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>246.5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>247.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>248.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>249.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>250.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>251.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>252.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>253.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>254.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>255.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>256.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>257.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>258.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>259.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>260.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>261.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>262.5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>263.5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>264.5</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>265.5</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>267.5</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>269.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>271.5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>273.5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>275.5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>277.5</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>280.5</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>281.5</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>282.5</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>283.5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>284.5</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>285.5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>286.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>287.5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>288.5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>289.5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>290.5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>291.5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>292.5</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>293.5</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>294.5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>295.5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>297.5</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>299.5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>301.5</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>306.5</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>311.5</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>316.5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>321.5</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>326.5</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>331.5</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>336.5</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>341.5</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>346.5</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>351.5</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>356.5</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>361.5</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>366.5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>371.5</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>376.5</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>381.5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>386.5</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>391.5</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>396.5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>401.5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>401.5</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>406.5</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>411.5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>416.5</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>421.5</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>426.5</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>436.5</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>446.5</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>456.5</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>466.5</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>476.5</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>486.5</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>496.5</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>506.5</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>516.5</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>526.5</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>536.5</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>546.5</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>556.5</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>566.5</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>576.5</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>596.5</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>616.5</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>636.5</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>656.5</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>676.5</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>726.5</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>776.5</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>826.5</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>876.5</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>976.5</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>1076.5</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>1176.5</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>1276.5</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1376.5</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1476.5</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1626.5</c:v>
+                <c:pt idx="79" formatCode="#,##0.00">
+                  <c:v>399.5</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="#,##0.00">
+                  <c:v>404.5</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="#,##0.00">
+                  <c:v>409.5</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="#,##0.00">
+                  <c:v>414.5</c:v>
+                </c:pt>
+                <c:pt idx="83" formatCode="#,##0.00">
+                  <c:v>419.5</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="#,##0.00">
+                  <c:v>424.5</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="#,##0.00">
+                  <c:v>434.5</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="#,##0.00">
+                  <c:v>444.5</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="#,##0.00">
+                  <c:v>454.5</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="#,##0.00">
+                  <c:v>464.5</c:v>
+                </c:pt>
+                <c:pt idx="89" formatCode="#,##0.00">
+                  <c:v>474.5</c:v>
+                </c:pt>
+                <c:pt idx="90" formatCode="#,##0.00">
+                  <c:v>484.5</c:v>
+                </c:pt>
+                <c:pt idx="91" formatCode="#,##0.00">
+                  <c:v>494.5</c:v>
+                </c:pt>
+                <c:pt idx="92" formatCode="#,##0.00">
+                  <c:v>504.5</c:v>
+                </c:pt>
+                <c:pt idx="93" formatCode="#,##0.00">
+                  <c:v>514.5</c:v>
+                </c:pt>
+                <c:pt idx="94" formatCode="#,##0.00">
+                  <c:v>524.5</c:v>
+                </c:pt>
+                <c:pt idx="95" formatCode="#,##0.00">
+                  <c:v>534.5</c:v>
+                </c:pt>
+                <c:pt idx="96" formatCode="#,##0.00">
+                  <c:v>544.5</c:v>
+                </c:pt>
+                <c:pt idx="97" formatCode="#,##0.00">
+                  <c:v>554.5</c:v>
+                </c:pt>
+                <c:pt idx="98" formatCode="#,##0.00">
+                  <c:v>564.5</c:v>
+                </c:pt>
+                <c:pt idx="99" formatCode="#,##0.00">
+                  <c:v>574.5</c:v>
+                </c:pt>
+                <c:pt idx="100" formatCode="#,##0.00">
+                  <c:v>594.5</c:v>
+                </c:pt>
+                <c:pt idx="101" formatCode="#,##0.00">
+                  <c:v>614.5</c:v>
+                </c:pt>
+                <c:pt idx="102" formatCode="#,##0.00">
+                  <c:v>634.5</c:v>
+                </c:pt>
+                <c:pt idx="103" formatCode="#,##0.00">
+                  <c:v>654.5</c:v>
+                </c:pt>
+                <c:pt idx="104" formatCode="#,##0.00">
+                  <c:v>674.5</c:v>
+                </c:pt>
+                <c:pt idx="105" formatCode="#,##0.00">
+                  <c:v>724.5</c:v>
+                </c:pt>
+                <c:pt idx="106" formatCode="#,##0.00">
+                  <c:v>774.5</c:v>
+                </c:pt>
+                <c:pt idx="107" formatCode="#,##0.00">
+                  <c:v>824.5</c:v>
+                </c:pt>
+                <c:pt idx="108" formatCode="#,##0.00">
+                  <c:v>874.5</c:v>
+                </c:pt>
+                <c:pt idx="109" formatCode="#,##0.00">
+                  <c:v>974.5</c:v>
+                </c:pt>
+                <c:pt idx="110" formatCode="#,##0.00">
+                  <c:v>1074.5</c:v>
+                </c:pt>
+                <c:pt idx="111" formatCode="#,##0.00">
+                  <c:v>1174.5</c:v>
+                </c:pt>
+                <c:pt idx="112" formatCode="#,##0.00">
+                  <c:v>1274.5</c:v>
+                </c:pt>
+                <c:pt idx="113" formatCode="#,##0.00">
+                  <c:v>1374.5</c:v>
+                </c:pt>
+                <c:pt idx="114" formatCode="#,##0.00">
+                  <c:v>1474.5</c:v>
+                </c:pt>
+                <c:pt idx="115" formatCode="#,##0.00">
+                  <c:v>1624.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2800,7 +2560,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2838,1002 +2598,6 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="928514991"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Dati!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>q</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Dati!$J$2:$J$130</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="129"/>
-                <c:pt idx="0">
-                  <c:v>232.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>233.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>234.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>235.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>236.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>237.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>238.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>239.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>240.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>241.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>242.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>243.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>244.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>245.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>246.5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>247.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>248.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>249.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>250.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>251.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>252.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>253.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>254.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>255.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>256.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>257.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>258.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>259.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>260.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>261.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>262.5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>263.5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>264.5</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>265.5</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>267.5</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>269.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>271.5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>273.5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>275.5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>277.5</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>280.5</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>281.5</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>282.5</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>283.5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>284.5</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>285.5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>286.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>287.5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>288.5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>289.5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>290.5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>291.5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>292.5</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>293.5</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>294.5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>295.5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>297.5</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>299.5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>301.5</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>306.5</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>311.5</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>316.5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>321.5</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>326.5</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>331.5</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>336.5</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>341.5</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>346.5</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>351.5</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>356.5</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>361.5</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>366.5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>371.5</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>376.5</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>381.5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>386.5</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>391.5</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>396.5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>401.5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>401.5</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>406.5</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>411.5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>416.5</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>421.5</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>426.5</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>436.5</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>446.5</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>456.5</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>466.5</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>476.5</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>486.5</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>496.5</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>506.5</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>516.5</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>526.5</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>536.5</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>546.5</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>556.5</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>566.5</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>576.5</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>596.5</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>616.5</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>636.5</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>656.5</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>676.5</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>726.5</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>776.5</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>826.5</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>876.5</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>976.5</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>1076.5</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>1176.5</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>1276.5</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1376.5</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1476.5</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1626.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Dati!$K$2:$K$130</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="129"/>
-                <c:pt idx="0">
-                  <c:v>1568.3956187495346</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1522.5370809527169</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1514.6242539025059</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1448.3063104970304</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1416.5366742321485</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1382.5913567979078</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1352.1281761548335</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1316.1424428014113</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1292.227285364251</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1256.5927696390497</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1229.4369333409034</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1216.4864065569802</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1177.9033231647918</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1160.0582035807654</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1133.0499991071747</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1126.0222379861807</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1106.6729262437348</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1086.0862804408871</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1064.1044902928011</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1047.7439145531227</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1026.778442658594</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1014.7575412000506</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>997.11005813176394</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>986.22185054767601</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>967.27810396229347</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>951.76583136790714</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>935.85143124581282</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>921.30762088650704</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>913.35673062950491</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>902.32259118873526</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>887.86164853068794</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>881.38319878055563</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>867.38188114877971</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>856.31606834535955</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>835.91280800603022</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>817.41771703364043</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>799.38993948084385</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>783.90908707552876</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>767.38704148583633</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>754.43717152141676</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>729.87584121464397</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>725.36750970623939</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>717.87462501523669</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>706.45534290239664</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>698.43410346668998</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>697.43410346668998</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>688.94979793160257</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>684.47166206396048</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>680.95909006382692</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>673.46326825153972</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>668.46311824386737</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>665.45383522701468</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>656.48955641615851</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>653.96694158426715</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>647.98130822981193</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>644.98126932838807</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>634.9664212342426</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>626.47768066658602</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>614.96584783011167</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>595.97345573965447</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>578.48887966849986</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>549</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>529</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>523</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>512</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>499</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>489</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>479</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>468</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>458</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>451</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>445</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>436</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>428</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>420</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>413</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>404</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>397</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>393</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>390</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>385</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>382</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>378</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>374</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>365</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>360</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>353</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>338</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>343</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>338</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>333</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>328</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>323</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>318</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>318</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>313</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>310</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>308</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>303</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>298</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>292</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>291</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>285</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>283</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>273</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>266</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>261</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>257</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>248</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>242</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>238</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>235</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>231</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>229</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>225</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-62F9-42E1-B5D8-74B8A0336C5B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="2060104288"/>
-        <c:axId val="2060102368"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="2060104288"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2060102368"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="2060102368"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2060104288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3970,46 +2734,6 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5597,522 +4321,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6223,42 +4431,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>479118</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>12539</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>316926</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>175846</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45B9704F-F8FD-4EC3-1599-453DF2735FF2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10829,7 +9001,7 @@
     <col min="8" max="10" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
@@ -10857,14 +9029,8 @@
       <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>251</v>
       </c>
@@ -10892,14 +9058,9 @@
       <c r="I2" s="1">
         <v>11.258330249197703</v>
       </c>
-      <c r="J2" s="1">
-        <v>232.5</v>
-      </c>
-      <c r="K2" s="8">
-        <v>1568.3956187495346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>252</v>
       </c>
@@ -10927,14 +9088,9 @@
       <c r="I3" s="1">
         <v>33.774990747593108</v>
       </c>
-      <c r="J3" s="1">
-        <v>233.5</v>
-      </c>
-      <c r="K3" s="8">
-        <v>1522.5370809527169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>253</v>
       </c>
@@ -10962,14 +9118,9 @@
       <c r="I4" s="1">
         <v>47.0540469389545</v>
       </c>
-      <c r="J4" s="1">
-        <v>234.5</v>
-      </c>
-      <c r="K4" s="8">
-        <v>1514.6242539025059</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>254</v>
       </c>
@@ -10997,14 +9148,9 @@
       <c r="I5" s="1">
         <v>43.878620458411561</v>
       </c>
-      <c r="J5" s="1">
-        <v>235.5</v>
-      </c>
-      <c r="K5" s="8">
-        <v>1448.3063104970304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>255</v>
       </c>
@@ -11032,14 +9178,9 @@
       <c r="I6" s="1">
         <v>40.414518843273804</v>
       </c>
-      <c r="J6" s="1">
-        <v>236.5</v>
-      </c>
-      <c r="K6" s="8">
-        <v>1416.5366742321485</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>256</v>
       </c>
@@ -11067,14 +9208,9 @@
       <c r="I7" s="1">
         <v>39.259818304894551</v>
       </c>
-      <c r="J7" s="1">
-        <v>237.5</v>
-      </c>
-      <c r="K7" s="8">
-        <v>1382.5913567979078</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>257</v>
       </c>
@@ -11102,14 +9238,9 @@
       <c r="I8" s="1">
         <v>38.393792901110118</v>
       </c>
-      <c r="J8" s="1">
-        <v>238.5</v>
-      </c>
-      <c r="K8" s="8">
-        <v>1352.1281761548335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>258</v>
       </c>
@@ -11137,14 +9268,9 @@
       <c r="I9" s="1">
         <v>30.02221399786054</v>
       </c>
-      <c r="J9" s="1">
-        <v>239.5</v>
-      </c>
-      <c r="K9" s="8">
-        <v>1316.1424428014113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>259</v>
       </c>
@@ -11172,14 +9298,9 @@
       <c r="I10" s="1">
         <v>28.290163190291665</v>
       </c>
-      <c r="J10" s="1">
-        <v>240.5</v>
-      </c>
-      <c r="K10" s="8">
-        <v>1292.227285364251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>260</v>
       </c>
@@ -11207,14 +9328,9 @@
       <c r="I11" s="1">
         <v>30.310889132455355</v>
       </c>
-      <c r="J11" s="1">
-        <v>241.5</v>
-      </c>
-      <c r="K11" s="8">
-        <v>1256.5927696390497</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>261</v>
       </c>
@@ -11242,14 +9358,9 @@
       <c r="I12" s="1">
         <v>23.671361036774659</v>
       </c>
-      <c r="J12" s="1">
-        <v>242.5</v>
-      </c>
-      <c r="K12" s="8">
-        <v>1229.4369333409034</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>262</v>
       </c>
@@ -11277,14 +9388,9 @@
       <c r="I13" s="1">
         <v>22.516660498395407</v>
       </c>
-      <c r="J13" s="1">
-        <v>243.5</v>
-      </c>
-      <c r="K13" s="8">
-        <v>1216.4864065569802</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>263</v>
       </c>
@@ -11312,14 +9418,9 @@
       <c r="I14" s="1">
         <v>23.96003617136947</v>
       </c>
-      <c r="J14" s="1">
-        <v>244.5</v>
-      </c>
-      <c r="K14" s="8">
-        <v>1177.9033231647918</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>264</v>
       </c>
@@ -11347,14 +9448,9 @@
       <c r="I15" s="1">
         <v>20.495934556231717</v>
       </c>
-      <c r="J15" s="1">
-        <v>245.5</v>
-      </c>
-      <c r="K15" s="8">
-        <v>1160.0582035807654</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>265</v>
       </c>
@@ -11382,14 +9478,9 @@
       <c r="I16" s="1">
         <v>20.495934556231717</v>
       </c>
-      <c r="J16" s="1">
-        <v>246.5</v>
-      </c>
-      <c r="K16" s="8">
-        <v>1133.0499991071747</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>266</v>
       </c>
@@ -11417,14 +9508,9 @@
       <c r="I17" s="1">
         <v>21.073284825421343</v>
       </c>
-      <c r="J17" s="1">
-        <v>247.5</v>
-      </c>
-      <c r="K17" s="8">
-        <v>1126.0222379861807</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>267</v>
       </c>
@@ -11452,14 +9538,9 @@
       <c r="I18" s="1">
         <v>17.320508075688775</v>
       </c>
-      <c r="J18" s="1">
-        <v>248.5</v>
-      </c>
-      <c r="K18" s="8">
-        <v>1106.6729262437348</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>268</v>
       </c>
@@ -11487,14 +9568,9 @@
       <c r="I19" s="1">
         <v>19.341234017852464</v>
       </c>
-      <c r="J19" s="1">
-        <v>249.5</v>
-      </c>
-      <c r="K19" s="8">
-        <v>1086.0862804408871</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>269</v>
       </c>
@@ -11522,14 +9598,9 @@
       <c r="I20" s="1">
         <v>18.763883748662838</v>
       </c>
-      <c r="J20" s="1">
-        <v>250.5</v>
-      </c>
-      <c r="K20" s="8">
-        <v>1064.1044902928011</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>270</v>
       </c>
@@ -11557,14 +9628,9 @@
       <c r="I21" s="1">
         <v>15.01110699893027</v>
       </c>
-      <c r="J21" s="1">
-        <v>251.5</v>
-      </c>
-      <c r="K21" s="8">
-        <v>1047.7439145531227</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>271</v>
       </c>
@@ -11592,14 +9658,9 @@
       <c r="I22" s="1">
         <v>13.856406460551019</v>
       </c>
-      <c r="J22" s="1">
-        <v>252.5</v>
-      </c>
-      <c r="K22" s="8">
-        <v>1026.778442658594</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>272</v>
       </c>
@@ -11627,14 +9688,9 @@
       <c r="I23" s="1">
         <v>14.433756729740645</v>
       </c>
-      <c r="J23" s="1">
-        <v>253.5</v>
-      </c>
-      <c r="K23" s="8">
-        <v>1014.7575412000506</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>273</v>
       </c>
@@ -11662,14 +9718,9 @@
       <c r="I24" s="1">
         <v>18.186533479473212</v>
       </c>
-      <c r="J24" s="1">
-        <v>254.5</v>
-      </c>
-      <c r="K24" s="8">
-        <v>997.11005813176394</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>274</v>
       </c>
@@ -11697,14 +9748,9 @@
       <c r="I25" s="1">
         <v>15.299782133525083</v>
       </c>
-      <c r="J25" s="1">
-        <v>255.5</v>
-      </c>
-      <c r="K25" s="8">
-        <v>986.22185054767601</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>275</v>
       </c>
@@ -11732,14 +9778,9 @@
       <c r="I26" s="1">
         <v>13.567731325956206</v>
       </c>
-      <c r="J26" s="1">
-        <v>256.5</v>
-      </c>
-      <c r="K26" s="8">
-        <v>967.27810396229347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>276</v>
       </c>
@@ -11767,14 +9808,9 @@
       <c r="I27" s="1">
         <v>13.856406460551019</v>
       </c>
-      <c r="J27" s="1">
-        <v>257.5</v>
-      </c>
-      <c r="K27" s="8">
-        <v>951.76583136790714</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>277</v>
       </c>
@@ -11802,14 +9838,9 @@
       <c r="I28" s="1">
         <v>10.96965511460289</v>
       </c>
-      <c r="J28" s="1">
-        <v>258.5</v>
-      </c>
-      <c r="K28" s="8">
-        <v>935.85143124581282</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>278</v>
       </c>
@@ -11837,14 +9868,9 @@
       <c r="I29" s="1">
         <v>12.413030787576954</v>
       </c>
-      <c r="J29" s="1">
-        <v>259.5</v>
-      </c>
-      <c r="K29" s="8">
-        <v>921.30762088650704</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>279</v>
       </c>
@@ -11872,14 +9898,9 @@
       <c r="I30" s="1">
         <v>10.680979980008077</v>
       </c>
-      <c r="J30" s="1">
-        <v>260.5</v>
-      </c>
-      <c r="K30" s="8">
-        <v>913.35673062950491</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>280</v>
       </c>
@@ -11907,14 +9928,9 @@
       <c r="I31" s="1">
         <v>11.835680518387329</v>
       </c>
-      <c r="J31" s="1">
-        <v>261.5</v>
-      </c>
-      <c r="K31" s="8">
-        <v>902.32259118873526</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>281</v>
       </c>
@@ -11942,14 +9958,9 @@
       <c r="I32" s="1">
         <v>10.392304845413264</v>
       </c>
-      <c r="J32" s="1">
-        <v>262.5</v>
-      </c>
-      <c r="K32" s="8">
-        <v>887.86164853068794</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>282</v>
       </c>
@@ -11977,14 +9988,9 @@
       <c r="I33" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J33" s="1">
-        <v>263.5</v>
-      </c>
-      <c r="K33" s="8">
-        <v>881.38319878055563</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>283</v>
       </c>
@@ -12012,14 +10018,9 @@
       <c r="I34" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J34" s="1">
-        <v>264.5</v>
-      </c>
-      <c r="K34" s="8">
-        <v>867.38188114877971</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>284</v>
       </c>
@@ -12047,14 +10048,9 @@
       <c r="I35" s="1">
         <v>11.835680518387329</v>
       </c>
-      <c r="J35" s="1">
-        <v>265.5</v>
-      </c>
-      <c r="K35" s="8">
-        <v>856.31606834535955</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>286</v>
       </c>
@@ -12082,14 +10078,9 @@
       <c r="I36" s="1">
         <v>8.0829037686547611</v>
       </c>
-      <c r="J36" s="1">
-        <v>267.5</v>
-      </c>
-      <c r="K36" s="8">
-        <v>835.91280800603022</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>288</v>
       </c>
@@ -12117,14 +10108,9 @@
       <c r="I37" s="1">
         <v>7.794228634059948</v>
       </c>
-      <c r="J37" s="1">
-        <v>269.5</v>
-      </c>
-      <c r="K37" s="8">
-        <v>817.41771703364043</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>290</v>
       </c>
@@ -12152,14 +10138,9 @@
       <c r="I38" s="1">
         <v>8.9489291724392004</v>
       </c>
-      <c r="J38" s="1">
-        <v>271.5</v>
-      </c>
-      <c r="K38" s="8">
-        <v>799.38993948084385</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>292</v>
       </c>
@@ -12187,14 +10168,9 @@
       <c r="I39" s="1">
         <v>8.0829037686547611</v>
       </c>
-      <c r="J39" s="1">
-        <v>273.5</v>
-      </c>
-      <c r="K39" s="8">
-        <v>783.90908707552876</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>294</v>
       </c>
@@ -12222,14 +10198,9 @@
       <c r="I40" s="1">
         <v>8.9489291724392004</v>
       </c>
-      <c r="J40" s="1">
-        <v>275.5</v>
-      </c>
-      <c r="K40" s="8">
-        <v>767.38704148583633</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>296</v>
       </c>
@@ -12257,14 +10228,9 @@
       <c r="I41" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J41" s="1">
-        <v>277.5</v>
-      </c>
-      <c r="K41" s="8">
-        <v>754.43717152141676</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>299</v>
       </c>
@@ -12292,14 +10258,9 @@
       <c r="I42" s="1">
         <v>9.2376043070340135</v>
       </c>
-      <c r="J42" s="1">
-        <v>280.5</v>
-      </c>
-      <c r="K42" s="8">
-        <v>729.87584121464397</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>300</v>
       </c>
@@ -12327,14 +10288,9 @@
       <c r="I43" s="1">
         <v>9.5262794416288248</v>
       </c>
-      <c r="J43" s="1">
-        <v>281.5</v>
-      </c>
-      <c r="K43" s="8">
-        <v>725.36750970623939</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>301</v>
       </c>
@@ -12362,14 +10318,9 @@
       <c r="I44" s="1">
         <v>9.2376043070340135</v>
       </c>
-      <c r="J44" s="1">
-        <v>282.5</v>
-      </c>
-      <c r="K44" s="8">
-        <v>717.87462501523669</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>302</v>
       </c>
@@ -12397,14 +10348,9 @@
       <c r="I45" s="1">
         <v>5.4848275573014451</v>
       </c>
-      <c r="J45" s="1">
-        <v>283.5</v>
-      </c>
-      <c r="K45" s="8">
-        <v>706.45534290239664</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>303</v>
       </c>
@@ -12432,14 +10378,9 @@
       <c r="I46" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J46" s="1">
-        <v>284.5</v>
-      </c>
-      <c r="K46" s="8">
-        <v>698.43410346668998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>304</v>
       </c>
@@ -12467,14 +10408,9 @@
       <c r="I47" s="1">
         <v>6.6395280956806966</v>
       </c>
-      <c r="J47" s="1">
-        <v>285.5</v>
-      </c>
-      <c r="K47" s="8">
-        <v>697.43410346668998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>305</v>
       </c>
@@ -12502,14 +10438,9 @@
       <c r="I48" s="1">
         <v>5.7735026918962582</v>
       </c>
-      <c r="J48" s="1">
-        <v>286.5</v>
-      </c>
-      <c r="K48" s="8">
-        <v>688.94979793160257</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>306</v>
       </c>
@@ -12537,14 +10468,9 @@
       <c r="I49" s="1">
         <v>4.3301270189221936</v>
       </c>
-      <c r="J49" s="1">
-        <v>287.5</v>
-      </c>
-      <c r="K49" s="8">
-        <v>684.47166206396048</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>307</v>
       </c>
@@ -12572,14 +10498,9 @@
       <c r="I50" s="1">
         <v>5.196152422706632</v>
       </c>
-      <c r="J50" s="1">
-        <v>288.5</v>
-      </c>
-      <c r="K50" s="8">
-        <v>680.95909006382692</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>308</v>
       </c>
@@ -12607,14 +10528,9 @@
       <c r="I51" s="1">
         <v>4.9074772881118189</v>
       </c>
-      <c r="J51" s="1">
-        <v>289.5</v>
-      </c>
-      <c r="K51" s="8">
-        <v>673.46326825153972</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>309</v>
       </c>
@@ -12642,14 +10558,9 @@
       <c r="I52" s="1">
         <v>4.9074772881118189</v>
       </c>
-      <c r="J52" s="1">
-        <v>290.5</v>
-      </c>
-      <c r="K52" s="8">
-        <v>668.46311824386737</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>310</v>
       </c>
@@ -12677,14 +10588,9 @@
       <c r="I53" s="1">
         <v>5.4848275573014451</v>
       </c>
-      <c r="J53" s="1">
-        <v>291.5</v>
-      </c>
-      <c r="K53" s="8">
-        <v>665.45383522701468</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>311</v>
       </c>
@@ -12712,14 +10618,9 @@
       <c r="I54" s="1">
         <v>2.598076211353316</v>
       </c>
-      <c r="J54" s="1">
-        <v>292.5</v>
-      </c>
-      <c r="K54" s="8">
-        <v>656.48955641615851</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>312</v>
       </c>
@@ -12747,14 +10648,9 @@
       <c r="I55" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J55" s="1">
-        <v>293.5</v>
-      </c>
-      <c r="K55" s="8">
-        <v>653.96694158426715</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>313</v>
       </c>
@@ -12782,14 +10678,9 @@
       <c r="I56" s="1">
         <v>3.4641016151377548</v>
       </c>
-      <c r="J56" s="1">
-        <v>294.5</v>
-      </c>
-      <c r="K56" s="8">
-        <v>647.98130822981193</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>314</v>
       </c>
@@ -12817,14 +10708,9 @@
       <c r="I57" s="1">
         <v>3.4641016151377548</v>
       </c>
-      <c r="J57" s="1">
-        <v>295.5</v>
-      </c>
-      <c r="K57" s="8">
-        <v>644.98126932838807</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>316</v>
       </c>
@@ -12852,14 +10738,9 @@
       <c r="I58" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J58" s="1">
-        <v>297.5</v>
-      </c>
-      <c r="K58" s="8">
-        <v>634.9664212342426</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>318</v>
       </c>
@@ -12887,14 +10768,9 @@
       <c r="I59" s="1">
         <v>3.7527767497325675</v>
       </c>
-      <c r="J59" s="1">
-        <v>299.5</v>
-      </c>
-      <c r="K59" s="8">
-        <v>626.47768066658602</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>320</v>
       </c>
@@ -12922,14 +10798,9 @@
       <c r="I60" s="1">
         <v>4.6188021535170067</v>
       </c>
-      <c r="J60" s="1">
-        <v>301.5</v>
-      </c>
-      <c r="K60" s="8">
-        <v>614.96584783011167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>325</v>
       </c>
@@ -12957,14 +10828,9 @@
       <c r="I61" s="1">
         <v>4.0414518843273806</v>
       </c>
-      <c r="J61" s="1">
-        <v>306.5</v>
-      </c>
-      <c r="K61" s="8">
-        <v>595.97345573965447</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>330</v>
       </c>
@@ -12992,14 +10858,9 @@
       <c r="I62" s="1">
         <v>2.598076211353316</v>
       </c>
-      <c r="J62" s="1">
-        <v>311.5</v>
-      </c>
-      <c r="K62" s="8">
-        <v>578.48887966849986</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>335</v>
       </c>
@@ -13024,14 +10885,9 @@
       <c r="I63" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J63" s="1">
-        <v>316.5</v>
-      </c>
-      <c r="K63" s="8">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>340</v>
       </c>
@@ -13056,14 +10912,9 @@
       <c r="I64" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J64" s="1">
-        <v>321.5</v>
-      </c>
-      <c r="K64" s="8">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>345</v>
       </c>
@@ -13088,14 +10939,9 @@
       <c r="I65" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J65" s="1">
-        <v>326.5</v>
-      </c>
-      <c r="K65" s="8">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>350</v>
       </c>
@@ -13120,14 +10966,9 @@
       <c r="I66" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J66" s="1">
-        <v>331.5</v>
-      </c>
-      <c r="K66" s="8">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>355</v>
       </c>
@@ -13152,14 +10993,9 @@
       <c r="I67" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J67" s="1">
-        <v>336.5</v>
-      </c>
-      <c r="K67" s="8">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>360</v>
       </c>
@@ -13184,14 +11020,9 @@
       <c r="I68" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J68" s="1">
-        <v>341.5</v>
-      </c>
-      <c r="K68" s="8">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>365</v>
       </c>
@@ -13216,14 +11047,9 @@
       <c r="I69" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J69" s="1">
-        <v>346.5</v>
-      </c>
-      <c r="K69" s="8">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>370</v>
       </c>
@@ -13248,14 +11074,9 @@
       <c r="I70" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J70" s="1">
-        <v>351.5</v>
-      </c>
-      <c r="K70" s="8">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>375</v>
       </c>
@@ -13280,14 +11101,9 @@
       <c r="I71" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J71" s="1">
-        <v>356.5</v>
-      </c>
-      <c r="K71" s="8">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>380</v>
       </c>
@@ -13312,14 +11128,9 @@
       <c r="I72" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J72" s="1">
-        <v>361.5</v>
-      </c>
-      <c r="K72" s="8">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>385</v>
       </c>
@@ -13344,14 +11155,9 @@
       <c r="I73" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J73" s="1">
-        <v>366.5</v>
-      </c>
-      <c r="K73" s="8">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>390</v>
       </c>
@@ -13376,14 +11182,9 @@
       <c r="I74" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J74" s="1">
-        <v>371.5</v>
-      </c>
-      <c r="K74" s="8">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>395</v>
       </c>
@@ -13408,14 +11209,9 @@
       <c r="I75" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J75" s="1">
-        <v>376.5</v>
-      </c>
-      <c r="K75" s="8">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>400</v>
       </c>
@@ -13440,14 +11236,9 @@
       <c r="I76" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J76" s="1">
-        <v>381.5</v>
-      </c>
-      <c r="K76" s="8">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>405</v>
       </c>
@@ -13472,14 +11263,9 @@
       <c r="I77" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J77" s="1">
-        <v>386.5</v>
-      </c>
-      <c r="K77" s="8">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>410</v>
       </c>
@@ -13504,14 +11290,9 @@
       <c r="I78" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J78" s="1">
-        <v>391.5</v>
-      </c>
-      <c r="K78" s="8">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>415</v>
       </c>
@@ -13536,14 +11317,8 @@
       <c r="I79" s="9">
         <v>0.11547005383792516</v>
       </c>
-      <c r="J79" s="1">
-        <v>396.5</v>
-      </c>
-      <c r="K79" s="8">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>420</v>
       </c>
@@ -13567,12 +11342,6 @@
       </c>
       <c r="I80" s="9">
         <v>0.11547005383792516</v>
-      </c>
-      <c r="J80" s="1">
-        <v>401.5</v>
-      </c>
-      <c r="K80" s="8">
-        <v>400</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13601,12 +11370,12 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="J81" s="1">
-        <f>F81-5</f>
-        <v>401.5</v>
+        <f>F81-7</f>
+        <v>399.5</v>
       </c>
       <c r="K81" s="6">
-        <f>G81-5</f>
-        <v>393</v>
+        <f>G81-7</f>
+        <v>391</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13635,12 +11404,12 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="J82" s="1">
-        <f t="shared" ref="J82:J117" si="0">F82-5</f>
-        <v>406.5</v>
+        <f t="shared" ref="J82:J117" si="0">F82-7</f>
+        <v>404.5</v>
       </c>
       <c r="K82" s="6">
-        <f t="shared" ref="K82:K117" si="1">G82-5</f>
-        <v>390</v>
+        <f t="shared" ref="K82:K117" si="1">G82-7</f>
+        <v>388</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13670,11 +11439,11 @@
       </c>
       <c r="J83" s="1">
         <f t="shared" si="0"/>
-        <v>411.5</v>
+        <v>409.5</v>
       </c>
       <c r="K83" s="6">
         <f t="shared" si="1"/>
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13704,11 +11473,11 @@
       </c>
       <c r="J84" s="1">
         <f t="shared" si="0"/>
-        <v>416.5</v>
+        <v>414.5</v>
       </c>
       <c r="K84" s="6">
         <f t="shared" si="1"/>
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13738,11 +11507,11 @@
       </c>
       <c r="J85" s="1">
         <f t="shared" si="0"/>
-        <v>421.5</v>
+        <v>419.5</v>
       </c>
       <c r="K85" s="6">
         <f t="shared" si="1"/>
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13772,11 +11541,11 @@
       </c>
       <c r="J86" s="1">
         <f t="shared" si="0"/>
-        <v>426.5</v>
+        <v>424.5</v>
       </c>
       <c r="K86" s="6">
         <f t="shared" si="1"/>
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13806,11 +11575,11 @@
       </c>
       <c r="J87" s="1">
         <f t="shared" si="0"/>
-        <v>436.5</v>
+        <v>434.5</v>
       </c>
       <c r="K87" s="6">
         <f t="shared" si="1"/>
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13840,11 +11609,11 @@
       </c>
       <c r="J88" s="1">
         <f t="shared" si="0"/>
-        <v>446.5</v>
+        <v>444.5</v>
       </c>
       <c r="K88" s="6">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13874,11 +11643,11 @@
       </c>
       <c r="J89" s="1">
         <f t="shared" si="0"/>
-        <v>456.5</v>
+        <v>454.5</v>
       </c>
       <c r="K89" s="6">
         <f t="shared" si="1"/>
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13908,11 +11677,11 @@
       </c>
       <c r="J90" s="1">
         <f t="shared" si="0"/>
-        <v>466.5</v>
+        <v>464.5</v>
       </c>
       <c r="K90" s="6">
         <f t="shared" si="1"/>
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13942,11 +11711,11 @@
       </c>
       <c r="J91" s="1">
         <f t="shared" si="0"/>
-        <v>476.5</v>
+        <v>474.5</v>
       </c>
       <c r="K91" s="6">
         <f t="shared" si="1"/>
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13976,11 +11745,11 @@
       </c>
       <c r="J92" s="1">
         <f t="shared" si="0"/>
-        <v>486.5</v>
+        <v>484.5</v>
       </c>
       <c r="K92" s="6">
         <f t="shared" si="1"/>
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14010,11 +11779,11 @@
       </c>
       <c r="J93" s="1">
         <f t="shared" si="0"/>
-        <v>496.5</v>
+        <v>494.5</v>
       </c>
       <c r="K93" s="6">
         <f t="shared" si="1"/>
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14044,11 +11813,11 @@
       </c>
       <c r="J94" s="1">
         <f t="shared" si="0"/>
-        <v>506.5</v>
+        <v>504.5</v>
       </c>
       <c r="K94" s="6">
         <f t="shared" si="1"/>
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14078,11 +11847,11 @@
       </c>
       <c r="J95" s="1">
         <f t="shared" si="0"/>
-        <v>516.5</v>
+        <v>514.5</v>
       </c>
       <c r="K95" s="6">
         <f t="shared" si="1"/>
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14112,11 +11881,11 @@
       </c>
       <c r="J96" s="1">
         <f t="shared" si="0"/>
-        <v>526.5</v>
+        <v>524.5</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="1"/>
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14146,11 +11915,11 @@
       </c>
       <c r="J97" s="1">
         <f t="shared" si="0"/>
-        <v>536.5</v>
+        <v>534.5</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="1"/>
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14180,11 +11949,11 @@
       </c>
       <c r="J98" s="1">
         <f t="shared" si="0"/>
-        <v>546.5</v>
+        <v>544.5</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="1"/>
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14214,11 +11983,11 @@
       </c>
       <c r="J99" s="1">
         <f t="shared" si="0"/>
-        <v>556.5</v>
+        <v>554.5</v>
       </c>
       <c r="K99" s="6">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14248,11 +12017,11 @@
       </c>
       <c r="J100" s="1">
         <f t="shared" si="0"/>
-        <v>566.5</v>
+        <v>564.5</v>
       </c>
       <c r="K100" s="6">
         <f t="shared" si="1"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14282,11 +12051,11 @@
       </c>
       <c r="J101" s="1">
         <f t="shared" si="0"/>
-        <v>576.5</v>
+        <v>574.5</v>
       </c>
       <c r="K101" s="6">
         <f t="shared" si="1"/>
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14316,11 +12085,11 @@
       </c>
       <c r="J102" s="1">
         <f t="shared" si="0"/>
-        <v>596.5</v>
+        <v>594.5</v>
       </c>
       <c r="K102" s="6">
         <f t="shared" si="1"/>
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14350,11 +12119,11 @@
       </c>
       <c r="J103" s="1">
         <f t="shared" si="0"/>
-        <v>616.5</v>
+        <v>614.5</v>
       </c>
       <c r="K103" s="6">
         <f t="shared" si="1"/>
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14384,11 +12153,11 @@
       </c>
       <c r="J104" s="1">
         <f t="shared" si="0"/>
-        <v>636.5</v>
+        <v>634.5</v>
       </c>
       <c r="K104" s="6">
         <f t="shared" si="1"/>
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14418,11 +12187,11 @@
       </c>
       <c r="J105" s="1">
         <f t="shared" si="0"/>
-        <v>656.5</v>
+        <v>654.5</v>
       </c>
       <c r="K105" s="6">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14452,11 +12221,11 @@
       </c>
       <c r="J106" s="1">
         <f t="shared" si="0"/>
-        <v>676.5</v>
+        <v>674.5</v>
       </c>
       <c r="K106" s="6">
         <f t="shared" si="1"/>
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14486,11 +12255,11 @@
       </c>
       <c r="J107" s="1">
         <f t="shared" si="0"/>
-        <v>726.5</v>
+        <v>724.5</v>
       </c>
       <c r="K107" s="6">
         <f t="shared" si="1"/>
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14520,11 +12289,11 @@
       </c>
       <c r="J108" s="1">
         <f t="shared" si="0"/>
-        <v>776.5</v>
+        <v>774.5</v>
       </c>
       <c r="K108" s="6">
         <f t="shared" si="1"/>
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14554,11 +12323,11 @@
       </c>
       <c r="J109" s="1">
         <f t="shared" si="0"/>
-        <v>826.5</v>
+        <v>824.5</v>
       </c>
       <c r="K109" s="6">
         <f t="shared" si="1"/>
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14588,11 +12357,11 @@
       </c>
       <c r="J110" s="1">
         <f t="shared" si="0"/>
-        <v>876.5</v>
+        <v>874.5</v>
       </c>
       <c r="K110" s="6">
         <f t="shared" si="1"/>
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14622,11 +12391,11 @@
       </c>
       <c r="J111" s="1">
         <f t="shared" si="0"/>
-        <v>976.5</v>
+        <v>974.5</v>
       </c>
       <c r="K111" s="6">
         <f t="shared" si="1"/>
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14656,11 +12425,11 @@
       </c>
       <c r="J112" s="1">
         <f t="shared" si="0"/>
-        <v>1076.5</v>
+        <v>1074.5</v>
       </c>
       <c r="K112" s="6">
         <f t="shared" si="1"/>
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14690,11 +12459,11 @@
       </c>
       <c r="J113" s="1">
         <f t="shared" si="0"/>
-        <v>1176.5</v>
+        <v>1174.5</v>
       </c>
       <c r="K113" s="6">
         <f t="shared" si="1"/>
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14724,11 +12493,11 @@
       </c>
       <c r="J114" s="1">
         <f t="shared" si="0"/>
-        <v>1276.5</v>
+        <v>1274.5</v>
       </c>
       <c r="K114" s="6">
         <f t="shared" si="1"/>
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14758,11 +12527,11 @@
       </c>
       <c r="J115" s="1">
         <f t="shared" si="0"/>
-        <v>1376.5</v>
+        <v>1374.5</v>
       </c>
       <c r="K115" s="6">
         <f t="shared" si="1"/>
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14792,11 +12561,11 @@
       </c>
       <c r="J116" s="1">
         <f t="shared" si="0"/>
-        <v>1476.5</v>
+        <v>1474.5</v>
       </c>
       <c r="K116" s="6">
         <f t="shared" si="1"/>
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14826,11 +12595,11 @@
       </c>
       <c r="J117" s="1">
         <f t="shared" si="0"/>
-        <v>1626.5</v>
+        <v>1624.5</v>
       </c>
       <c r="K117" s="6">
         <f t="shared" si="1"/>
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14877,9 +12646,7 @@
     <col min="1" max="2" width="12.44140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="5" width="12.44140625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625"/>
-    <col min="8" max="11" width="12.44140625" style="1" customWidth="1"/>
+    <col min="6" max="11" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -14901,7 +12668,7 @@
       <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -17189,8 +14956,8 @@
       <c r="F79" s="1">
         <v>396.5</v>
       </c>
-      <c r="G79" s="8">
-        <v>397</v>
+      <c r="G79" s="1">
+        <v>396</v>
       </c>
       <c r="H79" s="9">
         <v>0.11547005383792516</v>
@@ -17215,8 +14982,8 @@
       <c r="F80" s="1">
         <v>401.5</v>
       </c>
-      <c r="G80" s="8">
-        <v>400</v>
+      <c r="G80" s="1">
+        <v>393</v>
       </c>
       <c r="H80" s="9">
         <v>0.11547005383792516</v>
@@ -17239,10 +15006,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F81" s="1">
-        <v>401.5</v>
-      </c>
-      <c r="G81" s="6">
-        <v>393</v>
+        <v>406.5</v>
+      </c>
+      <c r="G81" s="1">
+        <v>391</v>
       </c>
       <c r="H81" s="9">
         <v>0.11547005383792516</v>
@@ -17265,10 +15032,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F82" s="1">
-        <v>406.5</v>
-      </c>
-      <c r="G82" s="6">
-        <v>390</v>
+        <v>411.5</v>
+      </c>
+      <c r="G82" s="1">
+        <v>388</v>
       </c>
       <c r="H82" s="9">
         <v>0.11547005383792516</v>
@@ -17291,10 +15058,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F83" s="1">
-        <v>411.5</v>
-      </c>
-      <c r="G83" s="6">
-        <v>385</v>
+        <v>416.5</v>
+      </c>
+      <c r="G83" s="1">
+        <v>383</v>
       </c>
       <c r="H83" s="9">
         <v>0.11547005383792516</v>
@@ -17317,10 +15084,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F84" s="1">
-        <v>416.5</v>
-      </c>
-      <c r="G84" s="6">
-        <v>382</v>
+        <v>421.5</v>
+      </c>
+      <c r="G84" s="1">
+        <v>380</v>
       </c>
       <c r="H84" s="9">
         <v>0.11547005383792516</v>
@@ -17343,10 +15110,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F85" s="1">
-        <v>421.5</v>
-      </c>
-      <c r="G85" s="6">
-        <v>378</v>
+        <v>426.5</v>
+      </c>
+      <c r="G85" s="1">
+        <v>376</v>
       </c>
       <c r="H85" s="9">
         <v>0.11547005383792516</v>
@@ -17369,10 +15136,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F86" s="1">
-        <v>426.5</v>
-      </c>
-      <c r="G86" s="6">
-        <v>374</v>
+        <v>431.5</v>
+      </c>
+      <c r="G86" s="1">
+        <v>372</v>
       </c>
       <c r="H86" s="9">
         <v>0.11547005383792516</v>
@@ -17395,10 +15162,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F87" s="1">
-        <v>436.5</v>
-      </c>
-      <c r="G87" s="6">
-        <v>365</v>
+        <v>441.5</v>
+      </c>
+      <c r="G87" s="1">
+        <v>363</v>
       </c>
       <c r="H87" s="9">
         <v>0.11547005383792516</v>
@@ -17421,10 +15188,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F88" s="1">
-        <v>446.5</v>
-      </c>
-      <c r="G88" s="6">
-        <v>360</v>
+        <v>451.5</v>
+      </c>
+      <c r="G88" s="1">
+        <v>358</v>
       </c>
       <c r="H88" s="9">
         <v>0.11547005383792516</v>
@@ -17447,10 +15214,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F89" s="1">
-        <v>456.5</v>
-      </c>
-      <c r="G89" s="6">
-        <v>353</v>
+        <v>461.5</v>
+      </c>
+      <c r="G89" s="1">
+        <v>351</v>
       </c>
       <c r="H89" s="9">
         <v>0.11547005383792516</v>
@@ -17473,10 +15240,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F90" s="1">
-        <v>466.5</v>
-      </c>
-      <c r="G90" s="6">
-        <v>338</v>
+        <v>471.5</v>
+      </c>
+      <c r="G90" s="1">
+        <v>336</v>
       </c>
       <c r="H90" s="9">
         <v>0.11547005383792516</v>
@@ -17499,10 +15266,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F91" s="1">
-        <v>476.5</v>
-      </c>
-      <c r="G91" s="6">
-        <v>343</v>
+        <v>481.5</v>
+      </c>
+      <c r="G91" s="1">
+        <v>341</v>
       </c>
       <c r="H91" s="9">
         <v>0.11547005383792516</v>
@@ -17525,10 +15292,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F92" s="1">
-        <v>486.5</v>
-      </c>
-      <c r="G92" s="6">
-        <v>338</v>
+        <v>491.5</v>
+      </c>
+      <c r="G92" s="1">
+        <v>336</v>
       </c>
       <c r="H92" s="9">
         <v>0.11547005383792516</v>
@@ -17551,10 +15318,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F93" s="1">
-        <v>496.5</v>
-      </c>
-      <c r="G93" s="6">
-        <v>333</v>
+        <v>501.5</v>
+      </c>
+      <c r="G93" s="1">
+        <v>331</v>
       </c>
       <c r="H93" s="9">
         <v>0.11547005383792516</v>
@@ -17577,10 +15344,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F94" s="1">
-        <v>506.5</v>
-      </c>
-      <c r="G94" s="6">
-        <v>328</v>
+        <v>511.5</v>
+      </c>
+      <c r="G94" s="1">
+        <v>326</v>
       </c>
       <c r="H94" s="9">
         <v>0.11547005383792516</v>
@@ -17603,10 +15370,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F95" s="1">
-        <v>516.5</v>
-      </c>
-      <c r="G95" s="6">
-        <v>323</v>
+        <v>521.5</v>
+      </c>
+      <c r="G95" s="1">
+        <v>321</v>
       </c>
       <c r="H95" s="9">
         <v>0.11547005383792516</v>
@@ -17629,10 +15396,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F96" s="1">
-        <v>526.5</v>
-      </c>
-      <c r="G96" s="6">
-        <v>318</v>
+        <v>531.5</v>
+      </c>
+      <c r="G96" s="1">
+        <v>316</v>
       </c>
       <c r="H96" s="9">
         <v>0.11547005383792516</v>
@@ -17655,10 +15422,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F97" s="1">
-        <v>536.5</v>
-      </c>
-      <c r="G97" s="6">
-        <v>318</v>
+        <v>541.5</v>
+      </c>
+      <c r="G97" s="1">
+        <v>316</v>
       </c>
       <c r="H97" s="9">
         <v>0.11547005383792516</v>
@@ -17681,10 +15448,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F98" s="1">
-        <v>546.5</v>
-      </c>
-      <c r="G98" s="6">
-        <v>313</v>
+        <v>551.5</v>
+      </c>
+      <c r="G98" s="1">
+        <v>311</v>
       </c>
       <c r="H98" s="9">
         <v>0.11547005383792516</v>
@@ -17707,10 +15474,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F99" s="1">
-        <v>556.5</v>
-      </c>
-      <c r="G99" s="6">
-        <v>310</v>
+        <v>561.5</v>
+      </c>
+      <c r="G99" s="1">
+        <v>308</v>
       </c>
       <c r="H99" s="9">
         <v>0.11547005383792516</v>
@@ -17733,10 +15500,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F100" s="1">
-        <v>566.5</v>
-      </c>
-      <c r="G100" s="6">
-        <v>308</v>
+        <v>571.5</v>
+      </c>
+      <c r="G100" s="1">
+        <v>306</v>
       </c>
       <c r="H100" s="9">
         <v>0.11547005383792516</v>
@@ -17759,10 +15526,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F101" s="1">
-        <v>576.5</v>
-      </c>
-      <c r="G101" s="6">
-        <v>303</v>
+        <v>581.5</v>
+      </c>
+      <c r="G101" s="1">
+        <v>301</v>
       </c>
       <c r="H101" s="9">
         <v>0.11547005383792516</v>
@@ -17785,10 +15552,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F102" s="1">
-        <v>596.5</v>
-      </c>
-      <c r="G102" s="6">
-        <v>298</v>
+        <v>601.5</v>
+      </c>
+      <c r="G102" s="1">
+        <v>296</v>
       </c>
       <c r="H102" s="9">
         <v>0.11547005383792516</v>
@@ -17811,10 +15578,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F103" s="1">
-        <v>616.5</v>
-      </c>
-      <c r="G103" s="6">
-        <v>292</v>
+        <v>621.5</v>
+      </c>
+      <c r="G103" s="1">
+        <v>290</v>
       </c>
       <c r="H103" s="9">
         <v>0.11547005383792516</v>
@@ -17837,10 +15604,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F104" s="1">
-        <v>636.5</v>
-      </c>
-      <c r="G104" s="6">
-        <v>291</v>
+        <v>641.5</v>
+      </c>
+      <c r="G104" s="1">
+        <v>289</v>
       </c>
       <c r="H104" s="9">
         <v>0.11547005383792516</v>
@@ -17863,10 +15630,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F105" s="1">
-        <v>656.5</v>
-      </c>
-      <c r="G105" s="6">
-        <v>285</v>
+        <v>661.5</v>
+      </c>
+      <c r="G105" s="1">
+        <v>283</v>
       </c>
       <c r="H105" s="9">
         <v>0.11547005383792516</v>
@@ -17889,10 +15656,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F106" s="1">
-        <v>676.5</v>
-      </c>
-      <c r="G106" s="6">
-        <v>283</v>
+        <v>681.5</v>
+      </c>
+      <c r="G106" s="1">
+        <v>281</v>
       </c>
       <c r="H106" s="9">
         <v>0.11547005383792516</v>
@@ -17915,10 +15682,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F107" s="1">
-        <v>726.5</v>
-      </c>
-      <c r="G107" s="6">
-        <v>273</v>
+        <v>731.5</v>
+      </c>
+      <c r="G107" s="1">
+        <v>271</v>
       </c>
       <c r="H107" s="9">
         <v>0.11547005383792516</v>
@@ -17941,10 +15708,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F108" s="1">
-        <v>776.5</v>
-      </c>
-      <c r="G108" s="6">
-        <v>266</v>
+        <v>781.5</v>
+      </c>
+      <c r="G108" s="1">
+        <v>264</v>
       </c>
       <c r="H108" s="9">
         <v>0.11547005383792516</v>
@@ -17967,10 +15734,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F109" s="1">
-        <v>826.5</v>
-      </c>
-      <c r="G109" s="6">
-        <v>261</v>
+        <v>831.5</v>
+      </c>
+      <c r="G109" s="1">
+        <v>259</v>
       </c>
       <c r="H109" s="9">
         <v>0.11547005383792516</v>
@@ -17993,10 +15760,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F110" s="1">
-        <v>876.5</v>
-      </c>
-      <c r="G110" s="6">
-        <v>257</v>
+        <v>881.5</v>
+      </c>
+      <c r="G110" s="1">
+        <v>255</v>
       </c>
       <c r="H110" s="9">
         <v>0.11547005383792516</v>
@@ -18019,10 +15786,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F111" s="1">
-        <v>976.5</v>
-      </c>
-      <c r="G111" s="6">
-        <v>248</v>
+        <v>981.5</v>
+      </c>
+      <c r="G111" s="1">
+        <v>246</v>
       </c>
       <c r="H111" s="9">
         <v>0.11547005383792516</v>
@@ -18045,10 +15812,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F112" s="1">
-        <v>1076.5</v>
-      </c>
-      <c r="G112" s="6">
-        <v>242</v>
+        <v>1081.5</v>
+      </c>
+      <c r="G112" s="1">
+        <v>240</v>
       </c>
       <c r="H112" s="9">
         <v>0.11547005383792516</v>
@@ -18071,10 +15838,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F113" s="1">
-        <v>1176.5</v>
-      </c>
-      <c r="G113" s="6">
-        <v>238</v>
+        <v>1181.5</v>
+      </c>
+      <c r="G113" s="1">
+        <v>236</v>
       </c>
       <c r="H113" s="9">
         <v>0.11547005383792516</v>
@@ -18097,10 +15864,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F114" s="1">
-        <v>1276.5</v>
-      </c>
-      <c r="G114" s="6">
-        <v>235</v>
+        <v>1281.5</v>
+      </c>
+      <c r="G114" s="1">
+        <v>233</v>
       </c>
       <c r="H114" s="9">
         <v>0.11547005383792516</v>
@@ -18123,10 +15890,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F115" s="1">
-        <v>1376.5</v>
-      </c>
-      <c r="G115" s="6">
-        <v>231</v>
+        <v>1381.5</v>
+      </c>
+      <c r="G115" s="1">
+        <v>229</v>
       </c>
       <c r="H115" s="9">
         <v>0.11547005383792516</v>
@@ -18149,10 +15916,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F116" s="1">
-        <v>1476.5</v>
-      </c>
-      <c r="G116" s="6">
-        <v>229</v>
+        <v>1481.5</v>
+      </c>
+      <c r="G116" s="1">
+        <v>227</v>
       </c>
       <c r="H116" s="9">
         <v>0.11547005383792516</v>
@@ -18175,10 +15942,10 @@
         <v>0.11547005383792516</v>
       </c>
       <c r="F117" s="1">
-        <v>1626.5</v>
-      </c>
-      <c r="G117" s="6">
-        <v>225</v>
+        <v>1631.5</v>
+      </c>
+      <c r="G117" s="1">
+        <v>223</v>
       </c>
       <c r="H117" s="9">
         <v>0.11547005383792516</v>
